--- a/docs/rollout/導入計畫.xlsx
+++ b/docs/rollout/導入計畫.xlsx
@@ -1262,7 +1262,7 @@
         <is>
           <t>⚠ 本文件為「模擬情境」之導入計畫，非實際產線導入紀錄。
 ・情境、數據與組織皆為假設；痛點來源為作者於元太科技之人工目檢經驗。
-・導入階段 ② PoC 已於模擬情境以檢驗規範 v1 執行（40 張半合成影像、3 位模擬 AI 評估者）：結果「未通過」Gate ②→③（漏判率 37.0%，目標 ≤ 5%；改善後重複性未量測）。
+・導入階段 ② PoC 已於模擬情境以檢驗規範 v1 執行（40 張半合成影像、3 位模擬 AI 評估者）：結果「未通過」Gate ②→③（漏判率 37.0%，目標 ≤ 5%；改善後重複性 77.5%，目標 ≥ 90%）。
 ・規範 v2 與 ② 重跑、③ 單線試行、④ 擴線與 MES 介接皆為「規劃」，尚未執行。數據出處：experiment/results/msa-summary.md</t>
         </is>
       </c>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="C11" s="15" t="inlineStr">
         <is>
-          <t>v0.2（草案）</t>
+          <t>v0.3（草案）</t>
         </is>
       </c>
       <c r="D11" s="1" t="n"/>
@@ -1639,11 +1639,21 @@
         </is>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="30" customHeight="1">
       <c r="A34" s="1" t="n"/>
-      <c r="B34" s="15" t="n"/>
-      <c r="C34" s="15" t="n"/>
-      <c r="D34" s="15" t="n"/>
+      <c r="B34" s="25" t="n">
+        <v>46301</v>
+      </c>
+      <c r="C34" s="15" t="inlineStr">
+        <is>
+          <t>回填 v1 第 2 次判定（補跑 169 次）：改善後重複性 77.5%，未達 ≥ 90% 門檻；KPI、Gate 紀錄、風險 R01／R12 與週會追蹤表同步更新</t>
+        </is>
+      </c>
+      <c r="D34" s="26" t="inlineStr">
+        <is>
+          <t>v0.3</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2043,13 +2053,13 @@
       </c>
       <c r="C23" s="26" t="inlineStr">
         <is>
-          <t>88.7%（71 組配對，第 2 次判定未完成）</t>
-        </is>
-      </c>
-      <c r="D23" s="26" t="inlineStr">
-        <is>
-          <t>未量測
-（API 額度耗盡）</t>
+          <t>85.8%（120 組配對）</t>
+        </is>
+      </c>
+      <c r="D23" s="35" t="inlineStr">
+        <is>
+          <t>77.5%（120 組配對）
+未達標</t>
         </is>
       </c>
       <c r="E23" s="36" t="inlineStr">
@@ -2639,7 +2649,7 @@
       </c>
       <c r="B55" s="15" t="inlineStr">
         <is>
-          <t>規範 v2 重跑之 API 預算可獲核准（v1 補跑約 US$1.2、v2 重跑約 US$3–4，模擬情境估算）</t>
+          <t>規範 v2 重跑之 API 預算可獲核准（v2 重跑約 US$3–4，模擬情境估算；v1 第 2 次判定已補跑，US$1.17）</t>
         </is>
       </c>
       <c r="C55" s="31" t="n"/>
@@ -4125,7 +4135,7 @@
       <c r="AR10" s="56" t="n"/>
       <c r="AS10" s="15" t="inlineStr">
         <is>
-          <t>Before 基準線。PoC 以模擬評估者示範：評估者間一致率 57.5%、漏判率 14.8%、人工複判率 42.5%、重複性 88.7%（實際導入須以作業員重測）</t>
+          <t>Before 基準線。PoC 以模擬評估者示範：評估者間一致率 57.5%、漏判率 14.8%、人工複判率 42.5%、重複性 85.8%（實際導入須以作業員重測）</t>
         </is>
       </c>
       <c r="AT10" s="57" t="inlineStr">
@@ -4692,7 +4702,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="64" customHeight="1">
+    <row r="16" ht="78" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
         <is>
           <t>2.3</t>
@@ -4776,7 +4786,7 @@
       <c r="AR16" s="56" t="n"/>
       <c r="AS16" s="65" t="inlineStr">
         <is>
-          <t>結果（模擬，120 筆）：漏判率 37.0%、評估者間一致率 60.0%、對標準答案一致率 60.8%、誤判率 3.0%、人工複判率 23.3%；重複性未量測（API 額度耗盡）→ 未達標</t>
+          <t>結果（模擬，120 筆）：漏判率 37.0%、評估者間一致率 60.0%、對標準答案一致率 60.8%、誤判率 3.0%、人工複判率 23.3%；第 2 次判定補跑後重複性 77.5%（改善前 85.8%）→ 未達標</t>
         </is>
       </c>
       <c r="AT16" s="35" t="inlineStr">
@@ -5064,7 +5074,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="50" customHeight="1">
+    <row r="20" ht="64" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
         <is>
           <t>2.7</t>
@@ -5247,7 +5257,7 @@
       </c>
       <c r="AS20" s="65" t="inlineStr">
         <is>
-          <t>結果：未通過。漏判率 37.0%（目標 ≤ 5%）、重複性未量測、預警提早 0 批。決議：不進入 ③；修訂規範 v2 並重跑 ②，③④ 順延 7 週</t>
+          <t>結果：未通過。漏判率 37.0%（目標 ≤ 5%）、重複性 77.5%（目標 ≥ 90%）、預警提早 0 批。決議：不進入 ③；修訂規範 v2 並重跑 ②，③④ 順延 7 週</t>
         </is>
       </c>
       <c r="AT20" s="35" t="inlineStr">
@@ -5455,7 +5465,7 @@
       </c>
       <c r="C23" s="15" t="inlineStr">
         <is>
-          <t>② 重跑：規範 v2 一致性分析（≥ 2 次判定，量測重複性）＋作者本人兩輪判定</t>
+          <t>② 重跑：規範 v2 一致性分析（≥ 2 次判定，量測重複性）；作者本人兩輪判定已於 v1 完成，v2 沿用同一表單再做</t>
         </is>
       </c>
       <c r="D23" s="26" t="inlineStr">
@@ -9316,7 +9326,7 @@
       </c>
       <c r="H5" s="15" t="inlineStr">
         <is>
-          <t>【已觸發】PoC v1（模擬）：漏判率 37.0%（10/27）；CHP 偵出率 14.8%、CRK 0%（被報成 SCR/CHP）；尺寸偏差 CHP 深度 −65%、CON 直徑 −57%、SCR 長度 +47%；Fleiss' kappa 0.39。原觸發條件：漏判率 &gt; 5% 或重複性 &lt; 90%</t>
+          <t>【已觸發】PoC v1（模擬）：漏判率 37.0%（10/27）；CHP 偵出率 14.8%、CRK 0%（被報成 SCR/CHP）；尺寸偏差 CHP 深度 −65%、CON 直徑 −57%、SCR 長度 +47%；Fleiss' kappa 0.39；重複性 77.5%（兩次不一致的 27 組中 15 組為量測跨過門檻、12 組為一次看到一次沒看到）。原觸發條件：漏判率 &gt; 5% 或重複性 &lt; 90%</t>
         </is>
       </c>
       <c r="I5" s="15" t="inlineStr">
@@ -10064,7 +10074,7 @@
       </c>
       <c r="H16" s="15" t="inlineStr">
         <is>
-          <t>【已觸發】PoC v1 執行中 API 額度耗盡（335 次呼叫、US$2.28），第 2 次判定未完成、改善後重複性未量測；v2 分塊放大後每顆約 36 次呼叫</t>
+          <t>【已觸發】PoC v1 執行中 API 額度耗盡（335 次呼叫、US$2.28），第 2 次判定中斷；加值後從快取補跑完成（共 504 次、US$3.46）；v2 分塊放大後每顆約 36 次呼叫</t>
         </is>
       </c>
       <c r="I16" s="15" t="inlineStr">
@@ -11026,7 +11036,7 @@
       </c>
       <c r="D9" s="15" t="inlineStr">
         <is>
-          <t>規範 v1 PoC：漏判率 37.0%（目標 ≤ 5%）、重複性未量測、預警提早 0 批 → 未通過</t>
+          <t>規範 v1 PoC：漏判率 37.0%（目標 ≤ 5%）、重複性 77.5%（目標 ≥ 90%）、預警提早 0 批 → 未通過</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
@@ -11074,7 +11084,7 @@
       </c>
       <c r="D10" s="15" t="inlineStr">
         <is>
-          <t>API 帳戶額度耗盡（v1 第 2 次判定未完成、改善後重複性未量測）；v2 分塊放大後每顆約 36 次呼叫，需加值並重估預算</t>
+          <t>v1 第 2 次判定已補跑完成（改善後重複性 77.5%）；v2 分塊放大後每顆約 36 次呼叫，需重估預算</t>
         </is>
       </c>
       <c r="E10" s="15" t="inlineStr">
@@ -11104,7 +11114,7 @@
       </c>
       <c r="K10" s="15" t="inlineStr">
         <is>
-          <t>預算申請已送直屬主管：v1 補跑約 US$1.2、v2 重跑約 US$3–4（模擬情境估算）；核准後從快取續跑</t>
+          <t>預算申請已送直屬主管：v2 重跑約 US$3–4（模擬情境估算）；核准後執行</t>
         </is>
       </c>
     </row>

--- a/docs/rollout/導入計畫.xlsx
+++ b/docs/rollout/導入計畫.xlsx
@@ -110,13 +110,13 @@
     <font>
       <name val="微軟正黑體"/>
       <b val="1"/>
-      <color rgb="009C0006"/>
+      <color rgb="00006100"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="微軟正黑體"/>
       <b val="1"/>
-      <color rgb="00006100"/>
+      <color rgb="009C0006"/>
       <sz val="10"/>
     </font>
     <font>
@@ -540,13 +540,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -626,7 +626,7 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="18" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1215,7 +1215,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1263,7 +1263,7 @@
           <t>⚠ 本文件為「模擬情境」之導入計畫，非實際產線導入紀錄。
 ・情境、數據與組織皆為假設；痛點來源為作者於元太科技之人工目檢經驗。
 ・導入階段 ② PoC 已於模擬情境以檢驗規範 v1 執行（40 張半合成影像、3 位模擬 AI 評估者）：結果「未通過」Gate ②→③（漏判率 37.0%，目標 ≤ 5%；改善後重複性 77.5%，目標 ≥ 90%）。
-・規範 v2 與 ② 重跑、③ 單線試行、④ 擴線與 MES 介接皆為「規劃」，尚未執行。數據出處：experiment/results/msa-summary.md</t>
+・規範 v2 已於作品中重跑一次（2026-10-07，同樣本、同評估者、240 筆）：漏判率 0%、重複性 92.5%、人工複判率 25.8% 達標；評估者間一致率 82.5%、誤判率 7.6% 未達，預警提早尚未以 v2 重驗 → Gate ②→③（v2）尚未通過。③ 單線試行、④ 擴線與 MES 介接仍為「規劃」。數據出處：experiment/results/msa-summary.md</t>
         </is>
       </c>
       <c r="C5" s="5" t="n"/>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="C11" s="15" t="inlineStr">
         <is>
-          <t>v0.3（草案）</t>
+          <t>v0.4（草案）</t>
         </is>
       </c>
       <c r="D11" s="1" t="n"/>
@@ -1448,12 +1448,12 @@
       </c>
       <c r="C20" s="15" t="inlineStr">
         <is>
-          <t>AI 辨識缺陷分類＋規則推導判定；一致性分析、p 管制圖預警。v1 漏判率 37.0%（CHP 偵出率 14.8%、CRK 0%、尺寸系統偏差）→ 規範 v2 修訂後重跑</t>
+          <t>AI 辨識缺陷分類＋規則推導判定；一致性分析、p 管制圖預警。v1 漏判率 37.0%（CHP 偵出率 14.8%、CRK 0%、尺寸系統偏差）→ 規範 v2 重跑：漏判率 0%、重複性 92.5%，但誤判率 7.6%</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>v1 已執行・未通過 Gate；v2 待重跑</t>
+          <t>v1 未通過 Gate；v2 已重跑・Gate 未通過</t>
         </is>
       </c>
     </row>
@@ -1652,6 +1652,22 @@
       <c r="D34" s="26" t="inlineStr">
         <is>
           <t>v0.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="1" t="n"/>
+      <c r="B35" s="25" t="n">
+        <v>46302</v>
+      </c>
+      <c r="C35" s="15" t="inlineStr">
+        <is>
+          <t>回填規範 v2 重跑結果（240 次、US$9.55）：漏判率 0%、重複性 92.5%、人工複判率 25.8% 達標；評估者間一致率 82.5%、誤判率 7.6% 未達，Gate（v2）未通過；新增 v2.1 對策</t>
+        </is>
+      </c>
+      <c r="D35" s="26" t="inlineStr">
+        <is>
+          <t>v0.4</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F72"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1992,8 +2008,8 @@
       </c>
       <c r="D21" s="13" t="inlineStr">
         <is>
-          <t>PoC v1 實測
-（After：檢驗規範 v1）</t>
+          <t>PoC 實測
+（規範 v1 → v2）</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
@@ -2025,8 +2041,8 @@
       </c>
       <c r="D22" s="35" t="inlineStr">
         <is>
-          <t>37.0%（10/27）
-未達標</t>
+          <t>37.0% → 0.0%（0/27）
+v2 達標</t>
         </is>
       </c>
       <c r="E22" s="36" t="inlineStr">
@@ -2058,8 +2074,8 @@
       </c>
       <c r="D23" s="35" t="inlineStr">
         <is>
-          <t>77.5%（120 組配對）
-未達標</t>
+          <t>77.5% → 92.5%（120 組配對）
+v2 達標</t>
         </is>
       </c>
       <c r="E23" s="36" t="inlineStr">
@@ -2089,10 +2105,10 @@
           <t>42.5%</t>
         </is>
       </c>
-      <c r="D24" s="37" t="inlineStr">
-        <is>
-          <t>23.3%（標準答案 22.5%）
-達標</t>
+      <c r="D24" s="35" t="inlineStr">
+        <is>
+          <t>23.3% → 25.8%（標準答案 22.5%）
+v2 達標</t>
         </is>
       </c>
       <c r="E24" s="36" t="inlineStr">
@@ -2122,10 +2138,10 @@
           <t>57.5%</t>
         </is>
       </c>
-      <c r="D25" s="35" t="inlineStr">
-        <is>
-          <t>60.0%
-未達標</t>
+      <c r="D25" s="37" t="inlineStr">
+        <is>
+          <t>60.0% → 82.5%
+v2 未達標</t>
         </is>
       </c>
       <c r="E25" s="36" t="inlineStr">
@@ -2155,10 +2171,10 @@
           <t>60.0%</t>
         </is>
       </c>
-      <c r="D26" s="35" t="inlineStr">
-        <is>
-          <t>60.8%
-未達標</t>
+      <c r="D26" s="37" t="inlineStr">
+        <is>
+          <t>60.8% → 75.8%
+v2 未達標</t>
         </is>
       </c>
       <c r="E26" s="36" t="inlineStr">
@@ -2188,9 +2204,10 @@
           <t>0.0%（0/66）</t>
         </is>
       </c>
-      <c r="D27" s="26" t="inlineStr">
-        <is>
-          <t>3.0%（2/66）</t>
+      <c r="D27" s="37" t="inlineStr">
+        <is>
+          <t>3.0% → 7.6%（5/66）
+v2 未達標</t>
         </is>
       </c>
       <c r="E27" s="36" t="inlineStr">
@@ -2220,10 +2237,10 @@
           <t>0 批（超出 UCL 才處理）</t>
         </is>
       </c>
-      <c r="D28" s="35" t="inlineStr">
-        <is>
-          <t>0 批（L24 預警＝異常；完美判定亦未提早）
-未達標</t>
+      <c r="D28" s="37" t="inlineStr">
+        <is>
+          <t>v1：0 批（L24 預警＝異常；完美判定亦未提早）
+v2：尚未重新驗證</t>
         </is>
       </c>
       <c r="E28" s="36" t="inlineStr">
@@ -2272,7 +2289,7 @@
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="38" t="inlineStr">
         <is>
-          <t>判讀（照實）：規範 v1 沒有讓判定明顯變準，漏判率反而由 14.8% 升至 37.0%，因此 ② Gate 未通過。</t>
+          <t>判讀（照實）：規範 v1 沒有讓判定明顯變準，漏判率反而由 14.8% 升至 37.0%，因此 ② Gate（v1）未通過；規範 v2 重跑後漏判率 0%、重複性 92.5%、人工複判率 25.8% 達標，但評估者間一致率 82.5%、誤判率 7.6% 未達，預警提早尚未重驗 → Gate（v2）尚未通過。</t>
         </is>
       </c>
       <c r="B30" s="1" t="n"/>
@@ -2308,7 +2325,7 @@
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="39" t="inlineStr">
         <is>
-          <t>・Fleiss' kappa 0.43 → 0.39，未改善；樣本少（每類 Fail 2–3 張），漏判 10/27 之 95% 信賴區間約 22–56%。</t>
+          <t>・Fleiss' kappa 0.43 → 0.39（v1）→ 0.82（v2）；樣本少（每類 Fail 2–3 張），v1 漏判 10/27 之 95% 信賴區間約 22–56%，v2 漏判 0/27 之上界約 13%。</t>
         </is>
       </c>
       <c r="B33" s="1" t="n"/>
@@ -2320,7 +2337,7 @@
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="39" t="inlineStr">
         <is>
-          <t>・對策：規範 v2（邊緣分塊放大檢查、以框選範圍換算尺寸、不確定一律送人工複判）＋ ② 重跑，見時程表 2.8–2.12。</t>
+          <t>・規範 v2（邊緣分塊放大檢查、以框選範圍換算尺寸、不確定一律送人工複判）已執行；新問題是 AI 框選過鬆、尺寸高估（CHP 深度 +147%），5 筆誤判全來自 S24、S31 兩張好晶粒。</t>
         </is>
       </c>
       <c r="B34" s="1" t="n"/>
@@ -2329,8 +2346,12 @@
       <c r="E34" s="1" t="n"/>
       <c r="F34" s="1" t="n"/>
     </row>
-    <row r="35">
-      <c r="A35" s="1" t="n"/>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="39" t="inlineStr">
+        <is>
+          <t>・下一輪 v2.1：程式在框內找缺陷實際邊緣再量測、量測值落在門檻 ±10% 內送人工複判、以 v2 實測誤差重跑管制圖模擬（時程表 2.11）。</t>
+        </is>
+      </c>
       <c r="B35" s="1" t="n"/>
       <c r="C35" s="1" t="n"/>
       <c r="D35" s="1" t="n"/>
@@ -2345,61 +2366,53 @@
       <c r="E36" s="1" t="n"/>
       <c r="F36" s="1" t="n"/>
     </row>
-    <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="29" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="1" t="n"/>
+      <c r="B37" s="1" t="n"/>
+      <c r="C37" s="1" t="n"/>
+      <c r="D37" s="1" t="n"/>
+      <c r="E37" s="1" t="n"/>
+      <c r="F37" s="1" t="n"/>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="29" t="inlineStr">
         <is>
           <t>4. 範圍</t>
         </is>
       </c>
-      <c r="B37" s="30" t="n"/>
-      <c r="C37" s="30" t="n"/>
-      <c r="D37" s="30" t="n"/>
-      <c r="E37" s="30" t="n"/>
-      <c r="F37" s="30" t="n"/>
-    </row>
-    <row r="38" ht="32" customHeight="1">
-      <c r="A38" s="13" t="inlineStr">
+      <c r="B38" s="30" t="n"/>
+      <c r="C38" s="30" t="n"/>
+      <c r="D38" s="30" t="n"/>
+      <c r="E38" s="30" t="n"/>
+      <c r="F38" s="30" t="n"/>
+    </row>
+    <row r="39" ht="32" customHeight="1">
+      <c r="A39" s="13" t="inlineStr">
         <is>
           <t>範圍內（In Scope）</t>
         </is>
       </c>
-      <c r="B38" s="32" t="n"/>
-      <c r="C38" s="33" t="n"/>
-      <c r="D38" s="13" t="inlineStr">
+      <c r="B39" s="32" t="n"/>
+      <c r="C39" s="33" t="n"/>
+      <c r="D39" s="13" t="inlineStr">
         <is>
           <t>不做什麼（Out of Scope）</t>
         </is>
       </c>
-      <c r="E38" s="32" t="n"/>
-      <c r="F38" s="33" t="n"/>
-    </row>
-    <row r="39" ht="30" customHeight="1">
-      <c r="A39" s="15" t="inlineStr">
-        <is>
-          <t>・僅限封裝段「晶粒外觀檢查站」；試行階段僅一條產線、一台取像站</t>
-        </is>
-      </c>
-      <c r="B39" s="31" t="n"/>
-      <c r="C39" s="31" t="n"/>
-      <c r="D39" s="15" t="inlineStr">
-        <is>
-          <t>✕ 不取代既有 AOI 機台或 Die Sorter；不改機台程式</t>
-        </is>
-      </c>
-      <c r="E39" s="31" t="n"/>
-      <c r="F39" s="31" t="n"/>
+      <c r="E39" s="32" t="n"/>
+      <c r="F39" s="33" t="n"/>
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="15" t="inlineStr">
         <is>
-          <t>・缺陷分類依檢驗規範：CHP 崩角、CRK 裂紋、SCR 刮傷、CON 污染（後續版本可擴充）</t>
+          <t>・僅限封裝段「晶粒外觀檢查站」；試行階段僅一條產線、一台取像站</t>
         </is>
       </c>
       <c r="B40" s="31" t="n"/>
       <c r="C40" s="31" t="n"/>
       <c r="D40" s="15" t="inlineStr">
         <is>
-          <t>✕ 不擴及其他站點（晶圓前段、Bump、Wire bond、成品外觀）</t>
+          <t>✕ 不取代既有 AOI 機台或 Die Sorter；不改機台程式</t>
         </is>
       </c>
       <c r="E40" s="31" t="n"/>
@@ -2408,14 +2421,14 @@
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="15" t="inlineStr">
         <is>
-          <t>・AI 僅辨識缺陷分類、尺寸與檢驗區域；判定由系統依允收標準推導並記錄規範版本（ADR-0001）</t>
+          <t>・缺陷分類依檢驗規範：CHP 崩角、CRK 裂紋、SCR 刮傷、CON 污染（後續版本可擴充）</t>
         </is>
       </c>
       <c r="B41" s="31" t="n"/>
       <c r="C41" s="31" t="n"/>
       <c r="D41" s="15" t="inlineStr">
         <is>
-          <t>✕ 不由 AI 直接給出判定，不讓 AI 自動放行或退件</t>
+          <t>✕ 不擴及其他站點（晶圓前段、Bump、Wire bond、成品外觀）</t>
         </is>
       </c>
       <c r="E41" s="31" t="n"/>
@@ -2424,14 +2437,14 @@
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="15" t="inlineStr">
         <is>
-          <t>・判定 Warning 送人工複判之流程與紀錄</t>
+          <t>・AI 僅辨識缺陷分類、尺寸與檢驗區域；判定由系統依允收標準推導並記錄規範版本（ADR-0001）</t>
         </is>
       </c>
       <c r="B42" s="31" t="n"/>
       <c r="C42" s="31" t="n"/>
       <c r="D42" s="15" t="inlineStr">
         <is>
-          <t>✕ 不自行訓練／標註深度學習模型（若 ③ 結果需要，另案評估）</t>
+          <t>✕ 不由 AI 直接給出判定，不讓 AI 自動放行或退件</t>
         </is>
       </c>
       <c r="E42" s="31" t="n"/>
@@ -2440,14 +2453,14 @@
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="15" t="inlineStr">
         <is>
-          <t>・批不良率 p 管制圖、判異規則預警、AI 草擬異常處置單（經人確認後送出）</t>
+          <t>・判定 Warning 送人工複判之流程與紀錄</t>
         </is>
       </c>
       <c r="B43" s="31" t="n"/>
       <c r="C43" s="31" t="n"/>
       <c r="D43" s="15" t="inlineStr">
         <is>
-          <t>✕ 不修改客戶出貨規格；檢驗規範僅能等於或嚴於客戶規格</t>
+          <t>✕ 不自行訓練／標註深度學習模型（若 ③ 結果需要，另案評估）</t>
         </is>
       </c>
       <c r="E43" s="31" t="n"/>
@@ -2456,100 +2469,96 @@
     <row r="44" ht="30" customHeight="1">
       <c r="A44" s="15" t="inlineStr">
         <is>
-          <t>・④ 階段：判定結果、缺陷代碼、規範版本與批號上拋 MES</t>
+          <t>・批不良率 p 管制圖、判異規則預警、AI 草擬異常處置單（經人確認後送出）</t>
         </is>
       </c>
       <c r="B44" s="31" t="n"/>
       <c r="C44" s="31" t="n"/>
       <c r="D44" s="15" t="inlineStr">
         <is>
-          <t>✕ 不由系統自動 Hold 批（MES Hold 仍由人依異常處置單執行）</t>
+          <t>✕ 不修改客戶出貨規格；檢驗規範僅能等於或嚴於客戶規格</t>
         </is>
       </c>
       <c r="E44" s="31" t="n"/>
       <c r="F44" s="31" t="n"/>
     </row>
     <row r="45" ht="30" customHeight="1">
-      <c r="A45" s="15" t="n"/>
+      <c r="A45" s="15" t="inlineStr">
+        <is>
+          <t>・④ 階段：判定結果、缺陷代碼、規範版本與批號上拋 MES</t>
+        </is>
+      </c>
       <c r="B45" s="31" t="n"/>
       <c r="C45" s="31" t="n"/>
       <c r="D45" s="15" t="inlineStr">
         <is>
-          <t>✕ 不作為作業員績效考核依據</t>
+          <t>✕ 不由系統自動 Hold 批（MES Hold 仍由人依異常處置單執行）</t>
         </is>
       </c>
       <c r="E45" s="31" t="n"/>
       <c r="F45" s="31" t="n"/>
     </row>
-    <row r="46">
-      <c r="A46" s="1" t="n"/>
-      <c r="B46" s="1" t="n"/>
-      <c r="C46" s="1" t="n"/>
-      <c r="D46" s="1" t="n"/>
-      <c r="E46" s="1" t="n"/>
-      <c r="F46" s="1" t="n"/>
-    </row>
-    <row r="47" ht="22" customHeight="1">
-      <c r="A47" s="29" t="inlineStr">
+    <row r="46" ht="30" customHeight="1">
+      <c r="A46" s="15" t="n"/>
+      <c r="B46" s="31" t="n"/>
+      <c r="C46" s="31" t="n"/>
+      <c r="D46" s="15" t="inlineStr">
+        <is>
+          <t>✕ 不作為作業員績效考核依據</t>
+        </is>
+      </c>
+      <c r="E46" s="31" t="n"/>
+      <c r="F46" s="31" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n"/>
+      <c r="B47" s="1" t="n"/>
+      <c r="C47" s="1" t="n"/>
+      <c r="D47" s="1" t="n"/>
+      <c r="E47" s="1" t="n"/>
+      <c r="F47" s="1" t="n"/>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="29" t="inlineStr">
         <is>
           <t>5. 主要假設與限制</t>
         </is>
       </c>
-      <c r="B47" s="30" t="n"/>
-      <c r="C47" s="30" t="n"/>
-      <c r="D47" s="30" t="n"/>
-      <c r="E47" s="30" t="n"/>
-      <c r="F47" s="30" t="n"/>
-    </row>
-    <row r="48" ht="32" customHeight="1">
-      <c r="A48" s="13" t="inlineStr">
+      <c r="B48" s="30" t="n"/>
+      <c r="C48" s="30" t="n"/>
+      <c r="D48" s="30" t="n"/>
+      <c r="E48" s="30" t="n"/>
+      <c r="F48" s="30" t="n"/>
+    </row>
+    <row r="49" ht="32" customHeight="1">
+      <c r="A49" s="13" t="inlineStr">
         <is>
           <t>編號</t>
         </is>
       </c>
-      <c r="B48" s="13" t="inlineStr">
+      <c r="B49" s="13" t="inlineStr">
         <is>
           <t>假設內容</t>
         </is>
       </c>
-      <c r="C48" s="32" t="n"/>
-      <c r="D48" s="32" t="n"/>
-      <c r="E48" s="33" t="n"/>
-      <c r="F48" s="13" t="inlineStr">
+      <c r="C49" s="32" t="n"/>
+      <c r="D49" s="32" t="n"/>
+      <c r="E49" s="33" t="n"/>
+      <c r="F49" s="13" t="inlineStr">
         <is>
           <t>驗證時點</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="30" customHeight="1">
-      <c r="A49" s="36" t="inlineStr">
-        <is>
-          <t>A1</t>
-        </is>
-      </c>
-      <c r="B49" s="15" t="inlineStr">
-        <is>
-          <t>試行線可加裝固定光源治具與取像站，影像解析度可達 5 µm/px（檢驗規範 v1 換算基準）</t>
-        </is>
-      </c>
-      <c r="C49" s="31" t="n"/>
-      <c r="D49" s="31" t="n"/>
-      <c r="E49" s="31" t="n"/>
-      <c r="F49" s="26" t="inlineStr">
-        <is>
-          <t>W3 取像條件定義</t>
         </is>
       </c>
     </row>
     <row r="50" ht="30" customHeight="1">
       <c r="A50" s="36" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="B50" s="15" t="inlineStr">
         <is>
-          <t>QA 可自產線挑選標準樣本並經量測確認標準答案；稀少缺陷（如 CRK）收集期可能延長</t>
+          <t>試行線可加裝固定光源治具與取像站，影像解析度可達 5 µm/px（檢驗規範 v1 換算基準）</t>
         </is>
       </c>
       <c r="C50" s="31" t="n"/>
@@ -2557,19 +2566,19 @@
       <c r="E50" s="31" t="n"/>
       <c r="F50" s="26" t="inlineStr">
         <is>
-          <t>W4 樣本收集</t>
+          <t>W3 取像條件定義</t>
         </is>
       </c>
     </row>
     <row r="51" ht="30" customHeight="1">
       <c r="A51" s="36" t="inlineStr">
         <is>
-          <t>A3</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="B51" s="15" t="inlineStr">
         <is>
-          <t>資安單位核可影像送外部 AI 服務（去識別化後）或核撥地端方案預算</t>
+          <t>QA 可自產線挑選標準樣本並經量測確認標準答案；稀少缺陷（如 CRK）收集期可能延長</t>
         </is>
       </c>
       <c r="C51" s="31" t="n"/>
@@ -2577,19 +2586,19 @@
       <c r="E51" s="31" t="n"/>
       <c r="F51" s="26" t="inlineStr">
         <is>
-          <t>W5 資安評估</t>
+          <t>W4 樣本收集</t>
         </is>
       </c>
     </row>
     <row r="52" ht="30" customHeight="1">
       <c r="A52" s="36" t="inlineStr">
         <is>
-          <t>A4</t>
+          <t>A3</t>
         </is>
       </c>
       <c r="B52" s="15" t="inlineStr">
         <is>
-          <t>③ 試行期間人工目檢照常執行，AI 判定不影響放行，僅作並行比對</t>
+          <t>資安單位核可影像送外部 AI 服務（去識別化後）或核撥地端方案預算</t>
         </is>
       </c>
       <c r="C52" s="31" t="n"/>
@@ -2597,19 +2606,19 @@
       <c r="E52" s="31" t="n"/>
       <c r="F52" s="26" t="inlineStr">
         <is>
-          <t>W19 試行啟動</t>
+          <t>W5 資安評估</t>
         </is>
       </c>
     </row>
     <row r="53" ht="30" customHeight="1">
       <c r="A53" s="36" t="inlineStr">
         <is>
-          <t>A5</t>
+          <t>A4</t>
         </is>
       </c>
       <c r="B53" s="15" t="inlineStr">
         <is>
-          <t>IT/MES 於第 19 週起可投入介接規格與開發資源（約 7 週）</t>
+          <t>③ 試行期間人工目檢照常執行，AI 判定不影響放行，僅作並行比對</t>
         </is>
       </c>
       <c r="C53" s="31" t="n"/>
@@ -2617,19 +2626,19 @@
       <c r="E53" s="31" t="n"/>
       <c r="F53" s="26" t="inlineStr">
         <is>
-          <t>W19 介接規格</t>
+          <t>W19 試行啟動</t>
         </is>
       </c>
     </row>
     <row r="54" ht="30" customHeight="1">
       <c r="A54" s="36" t="inlineStr">
         <is>
-          <t>A6</t>
+          <t>A5</t>
         </is>
       </c>
       <c r="B54" s="15" t="inlineStr">
         <is>
-          <t>PoC 之一致性分析以半合成樣本與模擬評估者完成（ADR-0002）；實際導入須以產線樣本與真人作業員重做</t>
+          <t>IT/MES 於第 19 週起可投入介接規格與開發資源（約 7 週）</t>
         </is>
       </c>
       <c r="C54" s="31" t="n"/>
@@ -2637,19 +2646,19 @@
       <c r="E54" s="31" t="n"/>
       <c r="F54" s="26" t="inlineStr">
         <is>
-          <t>① 階段 MSA</t>
+          <t>W19 介接規格</t>
         </is>
       </c>
     </row>
     <row r="55" ht="30" customHeight="1">
       <c r="A55" s="36" t="inlineStr">
         <is>
-          <t>A7</t>
+          <t>A6</t>
         </is>
       </c>
       <c r="B55" s="15" t="inlineStr">
         <is>
-          <t>規範 v2 重跑之 API 預算可獲核准（v2 重跑約 US$3–4，模擬情境估算；v1 第 2 次判定已補跑，US$1.17）</t>
+          <t>PoC 之一致性分析以半合成樣本與模擬評估者完成（ADR-0002）；實際導入須以產線樣本與真人作業員重做</t>
         </is>
       </c>
       <c r="C55" s="31" t="n"/>
@@ -2657,180 +2666,176 @@
       <c r="E55" s="31" t="n"/>
       <c r="F55" s="26" t="inlineStr">
         <is>
+          <t>① 階段 MSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="30" customHeight="1">
+      <c r="A56" s="36" t="inlineStr">
+        <is>
+          <t>A7</t>
+        </is>
+      </c>
+      <c r="B56" s="15" t="inlineStr">
+        <is>
+          <t>規範 v2 重跑之 API 預算可獲核准（v2 已於作品中重跑：實際 US$9.55／240 次呼叫，原估 US$3–4 低估；v1 第 2 次判定補跑 US$1.17）</t>
+        </is>
+      </c>
+      <c r="C56" s="31" t="n"/>
+      <c r="D56" s="31" t="n"/>
+      <c r="E56" s="31" t="n"/>
+      <c r="F56" s="26" t="inlineStr">
+        <is>
           <t>W14 預算核准</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="1" t="n"/>
-      <c r="B56" s="1" t="n"/>
-      <c r="C56" s="1" t="n"/>
-      <c r="D56" s="1" t="n"/>
-      <c r="E56" s="1" t="n"/>
-      <c r="F56" s="1" t="n"/>
-    </row>
-    <row r="57" ht="22" customHeight="1">
-      <c r="A57" s="29" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="1" t="n"/>
+      <c r="B57" s="1" t="n"/>
+      <c r="C57" s="1" t="n"/>
+      <c r="D57" s="1" t="n"/>
+      <c r="E57" s="1" t="n"/>
+      <c r="F57" s="1" t="n"/>
+    </row>
+    <row r="58" ht="22" customHeight="1">
+      <c r="A58" s="29" t="inlineStr">
         <is>
           <t>6. 專案成員與角色</t>
         </is>
       </c>
-      <c r="B57" s="30" t="n"/>
-      <c r="C57" s="30" t="n"/>
-      <c r="D57" s="30" t="n"/>
-      <c r="E57" s="30" t="n"/>
-      <c r="F57" s="30" t="n"/>
-    </row>
-    <row r="58" ht="32" customHeight="1">
-      <c r="A58" s="13" t="inlineStr">
+      <c r="B58" s="30" t="n"/>
+      <c r="C58" s="30" t="n"/>
+      <c r="D58" s="30" t="n"/>
+      <c r="E58" s="30" t="n"/>
+      <c r="F58" s="30" t="n"/>
+    </row>
+    <row r="59" ht="32" customHeight="1">
+      <c r="A59" s="13" t="inlineStr">
         <is>
           <t>角色</t>
         </is>
       </c>
-      <c r="B58" s="13" t="inlineStr">
+      <c r="B59" s="13" t="inlineStr">
         <is>
           <t>單位</t>
         </is>
       </c>
-      <c r="C58" s="13" t="inlineStr">
+      <c r="C59" s="13" t="inlineStr">
         <is>
           <t>主要職責</t>
         </is>
       </c>
-      <c r="D58" s="33" t="n"/>
-      <c r="E58" s="13" t="inlineStr">
+      <c r="D59" s="33" t="n"/>
+      <c r="E59" s="13" t="inlineStr">
         <is>
           <t>投入比例（預估）</t>
         </is>
       </c>
-      <c r="F58" s="13" t="inlineStr">
+      <c r="F59" s="13" t="inlineStr">
         <is>
           <t>備註</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="30" customHeight="1">
-      <c r="A59" s="34" t="inlineStr">
-        <is>
-          <t>專案發起人</t>
-        </is>
-      </c>
-      <c r="B59" s="26" t="inlineStr">
-        <is>
-          <t>製造處</t>
-        </is>
-      </c>
-      <c r="C59" s="15" t="inlineStr">
-        <is>
-          <t>核定章程與資源、Gate 審查最終簽核、跨部門議題裁決</t>
-        </is>
-      </c>
-      <c r="D59" s="31" t="n"/>
-      <c r="E59" s="26" t="inlineStr">
-        <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="F59" s="15" t="inlineStr">
-        <is>
-          <t>跨部門主管會議主席</t>
         </is>
       </c>
     </row>
     <row r="60" ht="30" customHeight="1">
       <c r="A60" s="34" t="inlineStr">
         <is>
-          <t>專案經理（專案專員）</t>
+          <t>專案發起人</t>
         </is>
       </c>
       <c r="B60" s="26" t="inlineStr">
         <is>
-          <t>智慧製造</t>
+          <t>製造處</t>
         </is>
       </c>
       <c r="C60" s="15" t="inlineStr">
         <is>
-          <t>時程與週會追蹤、PoC 建置、一致性分析、風險與升級管理</t>
+          <t>核定章程與資源、Gate 審查最終簽核、跨部門議題裁決</t>
         </is>
       </c>
       <c r="D60" s="31" t="n"/>
       <c r="E60" s="26" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="F60" s="15" t="inlineStr">
         <is>
-          <t>本文件撰寫人</t>
+          <t>跨部門主管會議主席</t>
         </is>
       </c>
     </row>
     <row r="61" ht="30" customHeight="1">
       <c r="A61" s="34" t="inlineStr">
         <is>
-          <t>品質代表</t>
+          <t>專案經理（專案專員）</t>
         </is>
       </c>
       <c r="B61" s="26" t="inlineStr">
         <is>
-          <t>QA/品保</t>
+          <t>智慧製造</t>
         </is>
       </c>
       <c r="C61" s="15" t="inlineStr">
         <is>
-          <t>標準樣本與標準答案、檢驗規範審查與發行、漏判風險把關</t>
+          <t>時程與週會追蹤、PoC 建置、一致性分析、風險與升級管理</t>
         </is>
       </c>
       <c r="D61" s="31" t="n"/>
       <c r="E61" s="26" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="F61" s="15" t="inlineStr">
         <is>
-          <t>規範 Owner</t>
+          <t>本文件撰寫人</t>
         </is>
       </c>
     </row>
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="34" t="inlineStr">
         <is>
-          <t>製程代表</t>
+          <t>品質代表</t>
         </is>
       </c>
       <c r="B62" s="26" t="inlineStr">
         <is>
-          <t>製程工程</t>
+          <t>QA/品保</t>
         </is>
       </c>
       <c r="C62" s="15" t="inlineStr">
         <is>
-          <t>允收標準技術依據、p 管制圖判異規則、異常處置單內容</t>
+          <t>標準樣本與標準答案、檢驗規範審查與發行、漏判風險把關</t>
         </is>
       </c>
       <c r="D62" s="31" t="n"/>
       <c r="E62" s="26" t="inlineStr">
         <is>
-          <t>20%</t>
-        </is>
-      </c>
-      <c r="F62" s="15" t="inlineStr"/>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="F62" s="15" t="inlineStr">
+        <is>
+          <t>規範 Owner</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="30" customHeight="1">
       <c r="A63" s="34" t="inlineStr">
         <is>
-          <t>設備代表</t>
+          <t>製程代表</t>
         </is>
       </c>
       <c r="B63" s="26" t="inlineStr">
         <is>
-          <t>設備工程</t>
+          <t>製程工程</t>
         </is>
       </c>
       <c r="C63" s="15" t="inlineStr">
         <is>
-          <t>光源治具與取像站、µm/px 校正、機台差異驗證</t>
+          <t>允收標準技術依據、p 管制圖判異規則、異常處置單內容</t>
         </is>
       </c>
       <c r="D63" s="31" t="n"/>
@@ -2839,161 +2844,169 @@
           <t>20%</t>
         </is>
       </c>
-      <c r="F63" s="15" t="inlineStr">
-        <is>
-          <t>治具請購協同採購</t>
-        </is>
-      </c>
+      <c r="F63" s="15" t="inlineStr"/>
     </row>
     <row r="64" ht="30" customHeight="1">
       <c r="A64" s="34" t="inlineStr">
         <is>
-          <t>系統代表</t>
+          <t>設備代表</t>
         </is>
       </c>
       <c r="B64" s="26" t="inlineStr">
         <is>
-          <t>IT/MES</t>
+          <t>設備工程</t>
         </is>
       </c>
       <c r="C64" s="15" t="inlineStr">
         <is>
-          <t>資安評估、PoC 環境、MES 介接開發與上線</t>
+          <t>光源治具與取像站、µm/px 校正、機台差異驗證</t>
         </is>
       </c>
       <c r="D64" s="31" t="n"/>
       <c r="E64" s="26" t="inlineStr">
         <is>
-          <t>20%（④ 階段 50%）</t>
-        </is>
-      </c>
-      <c r="F64" s="15" t="inlineStr"/>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="F64" s="15" t="inlineStr">
+        <is>
+          <t>治具請購協同採購</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="30" customHeight="1">
       <c r="A65" s="34" t="inlineStr">
         <is>
-          <t>產線代表</t>
+          <t>系統代表</t>
         </is>
       </c>
       <c r="B65" s="26" t="inlineStr">
         <is>
-          <t>生產/製造</t>
+          <t>IT/MES</t>
         </is>
       </c>
       <c r="C65" s="15" t="inlineStr">
         <is>
-          <t>目檢站作業員調度、並行比對執行、人工複判紀錄</t>
+          <t>資安評估、PoC 環境、MES 介接開發與上線</t>
         </is>
       </c>
       <c r="D65" s="31" t="n"/>
       <c r="E65" s="26" t="inlineStr">
         <is>
-          <t>15%</t>
-        </is>
-      </c>
-      <c r="F65" s="15" t="inlineStr">
-        <is>
-          <t>目檢站班長</t>
-        </is>
-      </c>
+          <t>20%（④ 階段 50%）</t>
+        </is>
+      </c>
+      <c r="F65" s="15" t="inlineStr"/>
     </row>
     <row r="66" ht="30" customHeight="1">
       <c r="A66" s="34" t="inlineStr">
         <is>
-          <t>生管代表</t>
+          <t>產線代表</t>
         </is>
       </c>
       <c r="B66" s="26" t="inlineStr">
         <is>
-          <t>生管</t>
+          <t>生產/製造</t>
         </is>
       </c>
       <c r="C66" s="15" t="inlineStr">
         <is>
-          <t>試行期產能與人力影響評估、批排程配合</t>
+          <t>目檢站作業員調度、並行比對執行、人工複判紀錄</t>
         </is>
       </c>
       <c r="D66" s="31" t="n"/>
       <c r="E66" s="26" t="inlineStr">
         <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="F66" s="15" t="inlineStr">
+        <is>
+          <t>目檢站班長</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="30" customHeight="1">
+      <c r="A67" s="34" t="inlineStr">
+        <is>
+          <t>生管代表</t>
+        </is>
+      </c>
+      <c r="B67" s="26" t="inlineStr">
+        <is>
+          <t>生管</t>
+        </is>
+      </c>
+      <c r="C67" s="15" t="inlineStr">
+        <is>
+          <t>試行期產能與人力影響評估、批排程配合</t>
+        </is>
+      </c>
+      <c r="D67" s="31" t="n"/>
+      <c r="E67" s="26" t="inlineStr">
+        <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="F66" s="15" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="1" t="n"/>
-      <c r="B67" s="1" t="n"/>
-      <c r="C67" s="1" t="n"/>
-      <c r="D67" s="1" t="n"/>
-      <c r="E67" s="1" t="n"/>
-      <c r="F67" s="1" t="n"/>
-    </row>
-    <row r="68" ht="22" customHeight="1">
-      <c r="A68" s="29" t="inlineStr">
+      <c r="F67" s="15" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="n"/>
+      <c r="B68" s="1" t="n"/>
+      <c r="C68" s="1" t="n"/>
+      <c r="D68" s="1" t="n"/>
+      <c r="E68" s="1" t="n"/>
+      <c r="F68" s="1" t="n"/>
+    </row>
+    <row r="69" ht="22" customHeight="1">
+      <c r="A69" s="29" t="inlineStr">
         <is>
           <t>7. 簽核</t>
         </is>
       </c>
-      <c r="B68" s="30" t="n"/>
-      <c r="C68" s="30" t="n"/>
-      <c r="D68" s="30" t="n"/>
-      <c r="E68" s="30" t="n"/>
-      <c r="F68" s="30" t="n"/>
-    </row>
-    <row r="69" ht="32" customHeight="1">
-      <c r="A69" s="13" t="inlineStr">
+      <c r="B69" s="30" t="n"/>
+      <c r="C69" s="30" t="n"/>
+      <c r="D69" s="30" t="n"/>
+      <c r="E69" s="30" t="n"/>
+      <c r="F69" s="30" t="n"/>
+    </row>
+    <row r="70" ht="32" customHeight="1">
+      <c r="A70" s="13" t="inlineStr">
         <is>
           <t>簽核角色</t>
         </is>
       </c>
-      <c r="B69" s="13" t="inlineStr">
+      <c r="B70" s="13" t="inlineStr">
         <is>
           <t>單位</t>
         </is>
       </c>
-      <c r="C69" s="13" t="inlineStr">
+      <c r="C70" s="13" t="inlineStr">
         <is>
           <t>姓名</t>
         </is>
       </c>
-      <c r="D69" s="13" t="inlineStr">
+      <c r="D70" s="13" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="E69" s="13" t="inlineStr">
+      <c r="E70" s="13" t="inlineStr">
         <is>
           <t>意見</t>
         </is>
       </c>
-      <c r="F69" s="33" t="n"/>
-    </row>
-    <row r="70" ht="26" customHeight="1">
-      <c r="A70" s="34" t="inlineStr">
-        <is>
-          <t>專案發起人</t>
-        </is>
-      </c>
-      <c r="B70" s="26" t="inlineStr">
-        <is>
-          <t>製造處</t>
-        </is>
-      </c>
-      <c r="C70" s="15" t="n"/>
-      <c r="D70" s="15" t="n"/>
-      <c r="E70" s="15" t="n"/>
       <c r="F70" s="33" t="n"/>
     </row>
     <row r="71" ht="26" customHeight="1">
       <c r="A71" s="34" t="inlineStr">
         <is>
-          <t>品質主管</t>
+          <t>專案發起人</t>
         </is>
       </c>
       <c r="B71" s="26" t="inlineStr">
         <is>
-          <t>QA/品保</t>
+          <t>製造處</t>
         </is>
       </c>
       <c r="C71" s="15" t="n"/>
@@ -3004,12 +3017,12 @@
     <row r="72" ht="26" customHeight="1">
       <c r="A72" s="34" t="inlineStr">
         <is>
-          <t>專案經理</t>
+          <t>品質主管</t>
         </is>
       </c>
       <c r="B72" s="26" t="inlineStr">
         <is>
-          <t>智慧製造</t>
+          <t>QA/品保</t>
         </is>
       </c>
       <c r="C72" s="15" t="n"/>
@@ -3017,16 +3030,32 @@
       <c r="E72" s="15" t="n"/>
       <c r="F72" s="33" t="n"/>
     </row>
+    <row r="73" ht="26" customHeight="1">
+      <c r="A73" s="34" t="inlineStr">
+        <is>
+          <t>專案經理</t>
+        </is>
+      </c>
+      <c r="B73" s="26" t="inlineStr">
+        <is>
+          <t>智慧製造</t>
+        </is>
+      </c>
+      <c r="C73" s="15" t="n"/>
+      <c r="D73" s="15" t="n"/>
+      <c r="E73" s="15" t="n"/>
+      <c r="F73" s="33" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="54">
+  <mergeCells count="55">
     <mergeCell ref="A41:C41"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="B49:E49"/>
     <mergeCell ref="C62:D62"/>
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="D41:F41"/>
+    <mergeCell ref="A46:C46"/>
     <mergeCell ref="E71:F71"/>
-    <mergeCell ref="C58:D58"/>
     <mergeCell ref="B55:E55"/>
     <mergeCell ref="B51:E51"/>
     <mergeCell ref="C64:D64"/>
@@ -3034,27 +3063,26 @@
     <mergeCell ref="D43:F43"/>
     <mergeCell ref="A33:F33"/>
     <mergeCell ref="A42:C42"/>
+    <mergeCell ref="E73:F73"/>
     <mergeCell ref="B50:E50"/>
     <mergeCell ref="C63:D63"/>
     <mergeCell ref="C65:D65"/>
     <mergeCell ref="A32:F32"/>
     <mergeCell ref="B54:E54"/>
-    <mergeCell ref="E69:F69"/>
+    <mergeCell ref="A35:F35"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B8:F8"/>
     <mergeCell ref="D39:F39"/>
     <mergeCell ref="B17:F17"/>
-    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="A43:C43"/>
     <mergeCell ref="B13:F13"/>
-    <mergeCell ref="A43:C43"/>
     <mergeCell ref="C59:D59"/>
     <mergeCell ref="D42:F42"/>
-    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="B56:E56"/>
     <mergeCell ref="A44:C44"/>
     <mergeCell ref="C60:D60"/>
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="B52:E52"/>
-    <mergeCell ref="B48:E48"/>
     <mergeCell ref="A31:F31"/>
     <mergeCell ref="A40:C40"/>
     <mergeCell ref="C61:D61"/>
@@ -3067,8 +3095,10 @@
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="B53:E53"/>
     <mergeCell ref="A45:C45"/>
+    <mergeCell ref="C67:D67"/>
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="E72:F72"/>
+    <mergeCell ref="D46:F46"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="D40:F40"/>
     <mergeCell ref="C66:D66"/>
@@ -4510,9 +4540,9 @@
       <c r="AQ13" s="56" t="n"/>
       <c r="AR13" s="56" t="n"/>
       <c r="AS13" s="64" t="inlineStr"/>
-      <c r="AT13" s="35" t="inlineStr">
-        <is>
-          <t>v1 未通過・v2 待重跑</t>
+      <c r="AT13" s="37" t="inlineStr">
+        <is>
+          <t>v1 未通過・v2 已重跑（Gate 未通過）</t>
         </is>
       </c>
     </row>
@@ -4696,7 +4726,7 @@
           <t>可離線執行之 PoC；判定附推導依據與 specVersion</t>
         </is>
       </c>
-      <c r="AT15" s="37" t="inlineStr">
+      <c r="AT15" s="35" t="inlineStr">
         <is>
           <t>已完成（模擬）</t>
         </is>
@@ -4789,7 +4819,7 @@
           <t>結果（模擬，120 筆）：漏判率 37.0%、評估者間一致率 60.0%、對標準答案一致率 60.8%、誤判率 3.0%、人工複判率 23.3%；第 2 次判定補跑後重複性 77.5%（改善前 85.8%）→ 未達標</t>
         </is>
       </c>
-      <c r="AT16" s="35" t="inlineStr">
+      <c r="AT16" s="37" t="inlineStr">
         <is>
           <t>完成・未達標</t>
         </is>
@@ -4882,7 +4912,7 @@
           <t>根因為 AI 偵測能力，非標準不一：CHP 偵出率 14.8%、CRK 0%（被報成 SCR/CHP）；尺寸系統偏差（CHP −65%、CON −57%、SCR +47%）</t>
         </is>
       </c>
-      <c r="AT17" s="37" t="inlineStr">
+      <c r="AT17" s="35" t="inlineStr">
         <is>
           <t>已完成（模擬）</t>
         </is>
@@ -4975,7 +5005,7 @@
           <t>結果：首次預警＝首次異常＝L24，提早 0 批（目標 ≥ 2 批，未達標）；無人工複判時漂移完全未被偵出</t>
         </is>
       </c>
-      <c r="AT18" s="35" t="inlineStr">
+      <c r="AT18" s="37" t="inlineStr">
         <is>
           <t>完成・未達標</t>
         </is>
@@ -5260,7 +5290,7 @@
           <t>結果：未通過。漏判率 37.0%（目標 ≤ 5%）、重複性 77.5%（目標 ≥ 90%）、預警提早 0 批。決議：不進入 ③；修訂規範 v2 並重跑 ②，③④ 順延 7 週</t>
         </is>
       </c>
-      <c r="AT20" s="35" t="inlineStr">
+      <c r="AT20" s="37" t="inlineStr">
         <is>
           <t>未通過</t>
         </is>
@@ -5353,9 +5383,9 @@
           <t>檢驗規範 v2（周邊區每邊 8 段 × 4 倍放大、核心區 4 象限；AI 只回缺陷代碼＋框選座標；線狀缺陷取嚴、≥ 4 顆 CON 送複判）</t>
         </is>
       </c>
-      <c r="AT21" s="66" t="inlineStr">
-        <is>
-          <t>提案完成・待執行</t>
+      <c r="AT21" s="35" t="inlineStr">
+        <is>
+          <t>已完成（作品，2026-10-07）</t>
         </is>
       </c>
     </row>
@@ -5446,13 +5476,13 @@
           <t>v2 PoC、預算核准單</t>
         </is>
       </c>
-      <c r="AT22" s="26" t="inlineStr">
-        <is>
-          <t>規劃・未執行</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="30" customHeight="1">
+      <c r="AT22" s="35" t="inlineStr">
+        <is>
+          <t>已完成（實際 US$9.55）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="78" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
         <is>
           <t>2.10</t>
@@ -5536,12 +5566,12 @@
       <c r="AR23" s="56" t="n"/>
       <c r="AS23" s="15" t="inlineStr">
         <is>
-          <t>v2 一致性分析報告（人 vs AI 對照）</t>
-        </is>
-      </c>
-      <c r="AT23" s="26" t="inlineStr">
-        <is>
-          <t>規劃・未執行</t>
+          <t>結果（作品，240 筆）：漏判率 0%、重複性 92.5%、人工複判率 25.8% 達標；評估者間一致率 82.5%、對標準答案一致率 75.8%、誤判率 7.6% 未達；Fleiss' kappa 0.82。作者本人 v2 判定尚未重做</t>
+        </is>
+      </c>
+      <c r="AT23" s="66" t="inlineStr">
+        <is>
+          <t>完成・部分達標</t>
         </is>
       </c>
     </row>
@@ -5638,7 +5668,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="50" customHeight="1">
+    <row r="25" ht="78" customHeight="1">
       <c r="A25" s="26" t="inlineStr">
         <is>
           <t>2.12</t>
@@ -5819,14 +5849,14 @@
         <f>IF(AR$4=$H25,"◆","")</f>
         <v/>
       </c>
-      <c r="AS25" s="34" t="inlineStr">
-        <is>
-          <t>Gate 標準：漏判率 ≤ 5%；重複性 ≥ 90%；人工複判率 ≤ 30%；評估者間一致率 ≥ 90%；預警提早 ≥ 2 批；資安核准；發起人簽核</t>
-        </is>
-      </c>
-      <c r="AT25" s="26" t="inlineStr">
-        <is>
-          <t>規劃・未執行</t>
+      <c r="AS25" s="65" t="inlineStr">
+        <is>
+          <t>Gate 標準：漏判率 ≤ 5%；重複性 ≥ 90%；人工複判率 ≤ 30%；評估者間一致率 ≥ 90%；預警提早 ≥ 2 批；資安核准；發起人簽核。作品現況：評估者間一致率 82.5%、誤判率 7.6% 未達、預警提早未重驗 → 未通過，轉規範 v2.1</t>
+        </is>
+      </c>
+      <c r="AT25" s="37" t="inlineStr">
+        <is>
+          <t>作品現況：未通過</t>
         </is>
       </c>
     </row>
@@ -9331,12 +9361,12 @@
       </c>
       <c r="I5" s="15" t="inlineStr">
         <is>
-          <t>AI 只回缺陷分類、判定由規則推導（ADR-0001）；規範 v2：邊緣分塊放大檢查、尺寸改由框選範圍換算、不確定一律送人工複判</t>
+          <t>AI 只回缺陷分類、判定由規則推導（ADR-0001）；規範 v2：邊緣分塊放大檢查、尺寸改由框選範圍換算、不確定一律送人工複判（已執行：漏判率 0%、重複性 92.5%，但框選過鬆使誤判率升至 7.6%）</t>
         </is>
       </c>
       <c r="J5" s="15" t="inlineStr">
         <is>
-          <t>② Gate 未通過、不進入 ③；執行規範 v2 並重跑 ②（時程表 2.8–2.12）</t>
+          <t>② Gate（v1、v2）皆未通過、不進入 ③；規範 v2.1：框內找實際邊緣再量測、門檻 ±10% 送人工複判</t>
         </is>
       </c>
       <c r="K5" s="26" t="inlineStr">
@@ -10074,7 +10104,7 @@
       </c>
       <c r="H16" s="15" t="inlineStr">
         <is>
-          <t>【已觸發】PoC v1 執行中 API 額度耗盡（335 次呼叫、US$2.28），第 2 次判定中斷；加值後從快取補跑完成（共 504 次、US$3.46）；v2 分塊放大後每顆約 36 次呼叫</t>
+          <t>【已觸發】PoC v1 執行中 API 額度耗盡（335 次呼叫、US$2.28），第 2 次判定中斷；加值後從快取補跑完成（共 504 次、US$3.46）；v2 重跑（240 次、US$9.55，原估 US$3–4）中再遇帳戶餘額不足與每月用量上限，兩次皆從快取續跑、無重複呼叫</t>
         </is>
       </c>
       <c r="I16" s="15" t="inlineStr">
@@ -11097,7 +11127,7 @@
       </c>
       <c r="G10" s="36" t="inlineStr">
         <is>
-          <t>卡關</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="H10" s="26" t="inlineStr">
@@ -11114,7 +11144,7 @@
       </c>
       <c r="K10" s="15" t="inlineStr">
         <is>
-          <t>預算申請已送直屬主管：v2 重跑約 US$3–4（模擬情境估算）；核准後執行</t>
+          <t>作品中已執行（2026-10-07）：36 張放大圖合併為每顆 1 次呼叫，實際 US$9.55；漏判率 0%、重複性 92.5%、誤判率 7.6% → Gate（v2）未通過，轉 v2.1</t>
         </is>
       </c>
     </row>

--- a/docs/rollout/導入計畫.xlsx
+++ b/docs/rollout/導入計畫.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="封面" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="專案章程" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="時程表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="RACI" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="風險清單" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="週會追蹤表" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="封面" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="專案章程" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="時程表" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RACI" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="風險清單" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="週會追蹤表" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'時程表'!$A$4:$K$41</definedName>
@@ -1215,7 +1215,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1261,7 +1261,7 @@
       <c r="B5" s="4" t="inlineStr">
         <is>
           <t>⚠ 本文件為「模擬情境」之導入計畫，非實際產線導入紀錄。
-・情境、數據與組織皆為假設；痛點來源為作者於元太科技之人工目檢經驗。
+・情境、數據與組織皆為假設；痛點來源為作者過去的目檢經驗（產線有檢驗規範，但判讀靠人眼）；人工基準線為作者本人照規範判兩輪（79 筆，真實）。
 ・導入階段 ② PoC 已於模擬情境以檢驗規範 v1 執行（40 張半合成影像、3 位模擬 AI 評估者）：結果「未通過」Gate ②→③（漏判率 37.0%，目標 ≤ 5%；改善後重複性 77.5%，目標 ≥ 90%）。
 ・規範 v2 已於作品中重跑一次（2026-10-07，同樣本、同評估者、240 筆）：漏判率 0%、重複性 92.5%、人工複判率 25.8% 達標；評估者間一致率 82.5%、誤判率 7.6% 未達，預警提早尚未以 v2 重驗 → Gate ②→③（v2）尚未通過。③ 單線試行、④ 擴線與 MES 介接仍為「規劃」。數據出處：experiment/results/msa-summary.md</t>
         </is>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="C11" s="15" t="inlineStr">
         <is>
-          <t>v0.4（草案）</t>
+          <t>v0.5（草案）</t>
         </is>
       </c>
       <c r="D11" s="1" t="n"/>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="D19" s="18" t="inlineStr">
         <is>
-          <t>模擬示範（規範 v1、口述標準 Before 一致性分析）</t>
+          <t>模擬示範（規範 v1、人工基準線：作者照規範判兩輪）</t>
         </is>
       </c>
     </row>
@@ -1668,6 +1668,22 @@
       <c r="D35" s="26" t="inlineStr">
         <is>
           <t>v0.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="1" t="n"/>
+      <c r="B36" s="25" t="n">
+        <v>46303</v>
+      </c>
+      <c r="C36" s="15" t="inlineStr">
+        <is>
+          <t>定位調整：痛點改為「有規範但判讀靠人眼」；KPI 基準線改為人眼＋規範（作者本人兩輪），新增每顆判讀時間（34.9 秒 → AI 8.2 秒）；任務 1.5 改為依現行規範的人工一致性分析</t>
+        </is>
+      </c>
+      <c r="D36" s="26" t="inlineStr">
+        <is>
+          <t>v0.5</t>
         </is>
       </c>
     </row>
@@ -1702,7 +1718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:F74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1892,12 +1908,12 @@
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="34" t="inlineStr">
         <is>
-          <t>判定標準不一</t>
+          <t>判讀靠人眼、速度慢</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>同一顆晶粒由不同作業員（或同一人不同時間）判定結果不同；允收標準多為口述標準，灰色地帶依個人經驗。</t>
+          <t>產線有檢驗規範，但每顆都要人眼找缺陷、量尺寸、對條文；作者照規範實測每顆 34.9 秒，檢驗站產能受限於人力。</t>
         </is>
       </c>
       <c r="C14" s="31" t="n"/>
@@ -1908,12 +1924,12 @@
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="34" t="inlineStr">
         <is>
-          <t>判定依據不可追溯</t>
+          <t>小缺陷漏看、量測因人而異</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>人工目檢僅記錄 Pass/Fail，缺陷分類與尺寸未結構化，客訴時無法回答「為什麼放行」。</t>
+          <t>人會疲勞，微小崩角、裂紋易漏看；門檻附近的量測不同人、不同次結果不同（作者照規範判兩輪：漏判率 23.5%、重複性 87.2%）。</t>
         </is>
       </c>
       <c r="C15" s="31" t="n"/>
@@ -1924,12 +1940,12 @@
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="34" t="inlineStr">
         <is>
-          <t>異常發現滯後</t>
+          <t>判定依據不可追溯</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>批不良率多於超出 UCL 或客退後才被注意，缺少趨勢型預警；處置依賴值班工程師個人經驗。</t>
+          <t>人工目檢僅記錄 Pass/Fail，缺陷分類與尺寸未結構化，客訴時無法回答「為什麼放行」。</t>
         </is>
       </c>
       <c r="C16" s="31" t="n"/>
@@ -1940,12 +1956,12 @@
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="34" t="inlineStr">
         <is>
-          <t>人工複判負荷</t>
+          <t>異常發現滯後</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>灰色地帶樣本大量送人工複判，複判工時與等待時間影響站點產出。</t>
+          <t>批不良率多於超出 UCL 或客退後才被注意，缺少趨勢型預警；處置依賴值班工程師個人經驗。</t>
         </is>
       </c>
       <c r="C17" s="31" t="n"/>
@@ -2003,7 +2019,7 @@
       <c r="C21" s="13" t="inlineStr">
         <is>
           <t>基準線
-（Before：口述標準）</t>
+（人眼＋規範：作者實測）</t>
         </is>
       </c>
       <c r="D21" s="13" t="inlineStr">
@@ -2026,282 +2042,303 @@
     <row r="22" ht="48" customHeight="1">
       <c r="A22" s="34" t="inlineStr">
         <is>
+          <t>每顆判讀時間</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>每顆晶粒完成判定所需時間（AI 為回應時間，不含取像）</t>
+        </is>
+      </c>
+      <c r="C22" s="26" t="inlineStr">
+        <is>
+          <t>34.9 秒（作者實測）</t>
+        </is>
+      </c>
+      <c r="D22" s="35" t="inlineStr">
+        <is>
+          <t>v2：8.2 秒
+比人工快約 4 倍</t>
+        </is>
+      </c>
+      <c r="E22" s="36" t="inlineStr">
+        <is>
+          <t>≤ 人工判讀時間</t>
+        </is>
+      </c>
+      <c r="F22" s="15" t="inlineStr">
+        <is>
+          <t>計時；試行期並行比對</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="48" customHeight="1">
+      <c r="A23" s="34" t="inlineStr">
+        <is>
           <t>漏判率</t>
         </is>
       </c>
-      <c r="B22" s="15" t="inlineStr">
+      <c r="B23" s="15" t="inlineStr">
         <is>
           <t>應 Fail 卻放行之比例</t>
         </is>
       </c>
-      <c r="C22" s="26" t="inlineStr">
-        <is>
-          <t>14.8%（4/27）</t>
-        </is>
-      </c>
-      <c r="D22" s="35" t="inlineStr">
+      <c r="C23" s="26" t="inlineStr">
+        <is>
+          <t>23.5%（4/17）</t>
+        </is>
+      </c>
+      <c r="D23" s="35" t="inlineStr">
         <is>
           <t>37.0% → 0.0%（0/27）
 v2 達標</t>
         </is>
       </c>
-      <c r="E22" s="36" t="inlineStr">
+      <c r="E23" s="36" t="inlineStr">
         <is>
           <t>≤ 5%</t>
         </is>
       </c>
-      <c r="F22" s="15" t="inlineStr">
+      <c r="F23" s="15" t="inlineStr">
         <is>
           <t>一致性分析；試行期並行比對</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="48" customHeight="1">
-      <c r="A23" s="34" t="inlineStr">
+    <row r="24" ht="48" customHeight="1">
+      <c r="A24" s="34" t="inlineStr">
         <is>
           <t>重複性</t>
         </is>
       </c>
-      <c r="B23" s="15" t="inlineStr">
+      <c r="B24" s="15" t="inlineStr">
         <is>
           <t>同一評估者對同一樣本兩次判定一致之比例</t>
         </is>
       </c>
-      <c r="C23" s="26" t="inlineStr">
-        <is>
-          <t>85.8%（120 組配對）</t>
-        </is>
-      </c>
-      <c r="D23" s="35" t="inlineStr">
+      <c r="C24" s="26" t="inlineStr">
+        <is>
+          <t>87.2%（39 組配對）</t>
+        </is>
+      </c>
+      <c r="D24" s="35" t="inlineStr">
         <is>
           <t>77.5% → 92.5%（120 組配對）
 v2 達標</t>
         </is>
       </c>
-      <c r="E23" s="36" t="inlineStr">
+      <c r="E24" s="36" t="inlineStr">
         <is>
           <t>≥ 90%</t>
         </is>
       </c>
-      <c r="F23" s="15" t="inlineStr">
+      <c r="F24" s="15" t="inlineStr">
         <is>
           <t>一致性分析（≥ 2 次判定）</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="48" customHeight="1">
-      <c r="A24" s="34" t="inlineStr">
+    <row r="25" ht="48" customHeight="1">
+      <c r="A25" s="34" t="inlineStr">
         <is>
           <t>人工複判率</t>
         </is>
       </c>
-      <c r="B24" s="15" t="inlineStr">
+      <c r="B25" s="15" t="inlineStr">
         <is>
           <t>判定 Warning 送人工複判之比例</t>
         </is>
       </c>
-      <c r="C24" s="26" t="inlineStr">
-        <is>
-          <t>42.5%</t>
-        </is>
-      </c>
-      <c r="D24" s="35" t="inlineStr">
+      <c r="C25" s="26" t="inlineStr">
+        <is>
+          <t>25.3%</t>
+        </is>
+      </c>
+      <c r="D25" s="35" t="inlineStr">
         <is>
           <t>23.3% → 25.8%（標準答案 22.5%）
 v2 達標</t>
         </is>
       </c>
-      <c r="E24" s="36" t="inlineStr">
+      <c r="E25" s="36" t="inlineStr">
         <is>
           <t>≤ 30%（規範 v2 提案門檻）</t>
         </is>
       </c>
-      <c r="F24" s="15" t="inlineStr">
+      <c r="F25" s="15" t="inlineStr">
         <is>
           <t>一致性分析；試行線週別統計</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="48" customHeight="1">
-      <c r="A25" s="34" t="inlineStr">
+    <row r="26" ht="48" customHeight="1">
+      <c r="A26" s="34" t="inlineStr">
         <is>
           <t>評估者間一致率（再現性）</t>
         </is>
       </c>
-      <c r="B25" s="15" t="inlineStr">
+      <c r="B26" s="15" t="inlineStr">
         <is>
           <t>三位評估者判定相同之樣本比例</t>
         </is>
       </c>
-      <c r="C25" s="26" t="inlineStr">
-        <is>
-          <t>57.5%</t>
-        </is>
-      </c>
-      <c r="D25" s="37" t="inlineStr">
+      <c r="C26" s="26" t="inlineStr">
+        <is>
+          <t>—（人工組僅 1 人）</t>
+        </is>
+      </c>
+      <c r="D26" s="37" t="inlineStr">
         <is>
           <t>60.0% → 82.5%
 v2 未達標</t>
         </is>
       </c>
-      <c r="E25" s="36" t="inlineStr">
+      <c r="E26" s="36" t="inlineStr">
         <is>
           <t>≥ 90%</t>
         </is>
       </c>
-      <c r="F25" s="15" t="inlineStr">
+      <c r="F26" s="15" t="inlineStr">
         <is>
           <t>一致性分析（計數值 MSA）</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="48" customHeight="1">
-      <c r="A26" s="34" t="inlineStr">
+    <row r="27" ht="48" customHeight="1">
+      <c r="A27" s="34" t="inlineStr">
         <is>
           <t>對標準答案一致率</t>
         </is>
       </c>
-      <c r="B26" s="15" t="inlineStr">
+      <c r="B27" s="15" t="inlineStr">
         <is>
           <t>判定與標準答案相符之比例（逐筆）</t>
         </is>
       </c>
-      <c r="C26" s="26" t="inlineStr">
-        <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="D26" s="37" t="inlineStr">
+      <c r="C27" s="26" t="inlineStr">
+        <is>
+          <t>70.9%</t>
+        </is>
+      </c>
+      <c r="D27" s="37" t="inlineStr">
         <is>
           <t>60.8% → 75.8%
 v2 未達標</t>
         </is>
       </c>
-      <c r="E26" s="36" t="inlineStr">
+      <c r="E27" s="36" t="inlineStr">
         <is>
           <t>≥ 90%</t>
         </is>
       </c>
-      <c r="F26" s="15" t="inlineStr">
+      <c r="F27" s="15" t="inlineStr">
         <is>
           <t>一致性分析</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="48" customHeight="1">
-      <c r="A27" s="34" t="inlineStr">
+    <row r="28" ht="48" customHeight="1">
+      <c r="A28" s="34" t="inlineStr">
         <is>
           <t>誤判率</t>
         </is>
       </c>
-      <c r="B27" s="15" t="inlineStr">
+      <c r="B28" s="15" t="inlineStr">
         <is>
           <t>應 Pass 卻退件之比例</t>
         </is>
       </c>
-      <c r="C27" s="26" t="inlineStr">
-        <is>
-          <t>0.0%（0/66）</t>
-        </is>
-      </c>
-      <c r="D27" s="37" t="inlineStr">
+      <c r="C28" s="26" t="inlineStr">
+        <is>
+          <t>2.3%（1/43）</t>
+        </is>
+      </c>
+      <c r="D28" s="37" t="inlineStr">
         <is>
           <t>3.0% → 7.6%（5/66）
 v2 未達標</t>
         </is>
       </c>
-      <c r="E27" s="36" t="inlineStr">
+      <c r="E28" s="36" t="inlineStr">
         <is>
           <t>≤ 3%（假設值，待 QA 核定）</t>
         </is>
       </c>
-      <c r="F27" s="15" t="inlineStr">
+      <c r="F28" s="15" t="inlineStr">
         <is>
           <t>一致性分析；試行期並行比對</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="48" customHeight="1">
-      <c r="A28" s="34" t="inlineStr">
+    <row r="29" ht="48" customHeight="1">
+      <c r="A29" s="34" t="inlineStr">
         <is>
           <t>異常提早發現批數</t>
         </is>
       </c>
-      <c r="B28" s="15" t="inlineStr">
+      <c r="B29" s="15" t="inlineStr">
         <is>
           <t>首次預警批 較 首次超出 UCL 批 提早之批數</t>
         </is>
       </c>
-      <c r="C28" s="26" t="inlineStr">
+      <c r="C29" s="26" t="inlineStr">
         <is>
           <t>0 批（超出 UCL 才處理）</t>
         </is>
       </c>
-      <c r="D28" s="37" t="inlineStr">
+      <c r="D29" s="37" t="inlineStr">
         <is>
           <t>v1：0 批（L24 預警＝異常；完美判定亦未提早）
 v2：尚未重新驗證</t>
         </is>
       </c>
-      <c r="E28" s="36" t="inlineStr">
+      <c r="E29" s="36" t="inlineStr">
         <is>
           <t>提早 ≥ 2 批</t>
         </is>
       </c>
-      <c r="F28" s="15" t="inlineStr">
+      <c r="F29" s="15" t="inlineStr">
         <is>
           <t>p 管制圖判異規則（25 批漂移情境模擬）</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="48" customHeight="1">
-      <c r="A29" s="34" t="inlineStr">
+    <row r="30" ht="48" customHeight="1">
+      <c r="A30" s="34" t="inlineStr">
         <is>
           <t>異常處置單確認時效</t>
         </is>
       </c>
-      <c r="B29" s="15" t="inlineStr">
+      <c r="B30" s="15" t="inlineStr">
         <is>
           <t>預警觸發至處置單經人確認送出之時間</t>
         </is>
       </c>
-      <c r="C29" s="26" t="inlineStr">
+      <c r="C30" s="26" t="inlineStr">
         <is>
           <t>未量測</t>
         </is>
       </c>
-      <c r="D29" s="26" t="inlineStr">
+      <c r="D30" s="26" t="inlineStr">
         <is>
           <t>未量測（PoC 未實作）</t>
         </is>
       </c>
-      <c r="E29" s="36" t="inlineStr">
+      <c r="E30" s="36" t="inlineStr">
         <is>
           <t>≤ 4 小時（假設值）</t>
         </is>
       </c>
-      <c r="F29" s="15" t="inlineStr">
+      <c r="F30" s="15" t="inlineStr">
         <is>
           <t>系統時間戳記</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="38" t="inlineStr">
-        <is>
-          <t>判讀（照實）：規範 v1 沒有讓判定明顯變準，漏判率反而由 14.8% 升至 37.0%，因此 ② Gate（v1）未通過；規範 v2 重跑後漏判率 0%、重複性 92.5%、人工複判率 25.8% 達標，但評估者間一致率 82.5%、誤判率 7.6% 未達，預警提早尚未重驗 → Gate（v2）尚未通過。</t>
-        </is>
-      </c>
-      <c r="B30" s="1" t="n"/>
-      <c r="C30" s="1" t="n"/>
-      <c r="D30" s="1" t="n"/>
-      <c r="E30" s="1" t="n"/>
-      <c r="F30" s="1" t="n"/>
-    </row>
     <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="39" t="inlineStr">
-        <is>
-          <t>・改善前漏判率低，是因為大量判 Warning、把 Fail 推給人工複判（42.5%），並非判定較準；v1 讓人工複判率回到 23.3%，緩衝也隨之消失。</t>
+      <c r="A31" s="38" t="inlineStr">
+        <is>
+          <t>判讀（照實）：規範 v1 的 AI 漏判率 37.0%，比人工 23.5% 還高，② Gate（v1）未通過；規範 v2 重跑後 AI 每顆 8.2 秒（人工 34.9 秒）、漏判率 0%、重複性 92.5%、人工複判率 25.8% 達標，但評估者間一致率 82.5%、誤判率 7.6%（人工 2.3%）未達，預警提早尚未重驗 → Gate（v2）尚未通過。</t>
         </is>
       </c>
       <c r="B31" s="1" t="n"/>
@@ -2313,7 +2350,7 @@
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="39" t="inlineStr">
         <is>
-          <t>・漏判主因是 AI「看不到」：CHP 偵出率 14.8%、CRK 0%；尺寸量測有系統性偏差（CHP 深度 −65%、CON 直徑 −57%、SCR 長度 +47%）。</t>
+          <t>・基準線為作者本人照規範判兩輪（79 筆，真實），只有一人且為規範撰寫者；試行期須以 3 位檢驗員重測。另一對照：只給 AI 口述標準時評估者間一致率 57.5%、人工複判率 42.5%，說明 AI 必須搭配規則。</t>
         </is>
       </c>
       <c r="B32" s="1" t="n"/>
@@ -2325,7 +2362,7 @@
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="39" t="inlineStr">
         <is>
-          <t>・Fleiss' kappa 0.43 → 0.39（v1）→ 0.82（v2）；樣本少（每類 Fail 2–3 張），v1 漏判 10/27 之 95% 信賴區間約 22–56%，v2 漏判 0/27 之上界約 13%。</t>
+          <t>・漏判主因是 AI「看不到」：CHP 偵出率 14.8%、CRK 0%；尺寸量測有系統性偏差（CHP 深度 −65%、CON 直徑 −57%、SCR 長度 +47%）。</t>
         </is>
       </c>
       <c r="B33" s="1" t="n"/>
@@ -2337,7 +2374,7 @@
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="39" t="inlineStr">
         <is>
-          <t>・規範 v2（邊緣分塊放大檢查、以框選範圍換算尺寸、不確定一律送人工複判）已執行；新問題是 AI 框選過鬆、尺寸高估（CHP 深度 +147%），5 筆誤判全來自 S24、S31 兩張好晶粒。</t>
+          <t>・Fleiss' kappa 0.43 → 0.39（v1）→ 0.82（v2）；樣本少（每類 Fail 2–3 張），v1 漏判 10/27 之 95% 信賴區間約 22–56%，v2 漏判 0/27 之上界約 13%。</t>
         </is>
       </c>
       <c r="B34" s="1" t="n"/>
@@ -2349,7 +2386,7 @@
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="39" t="inlineStr">
         <is>
-          <t>・下一輪 v2.1：程式在框內找缺陷實際邊緣再量測、量測值落在門檻 ±10% 內送人工複判、以 v2 實測誤差重跑管制圖模擬（時程表 2.11）。</t>
+          <t>・規範 v2（邊緣分塊放大檢查、以框選範圍換算尺寸、不確定一律送人工複判）已執行；新問題是 AI 框選過鬆、尺寸高估（CHP 深度 +147%），5 筆誤判全來自 S24、S31 兩張好晶粒。</t>
         </is>
       </c>
       <c r="B35" s="1" t="n"/>
@@ -2358,8 +2395,12 @@
       <c r="E35" s="1" t="n"/>
       <c r="F35" s="1" t="n"/>
     </row>
-    <row r="36">
-      <c r="A36" s="1" t="n"/>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="39" t="inlineStr">
+        <is>
+          <t>・下一輪 v2.1：程式在框內找缺陷實際邊緣再量測、量測值落在門檻 ±10% 內送人工複判、以 v2 實測誤差重跑管制圖模擬（時程表 2.11）。</t>
+        </is>
+      </c>
       <c r="B36" s="1" t="n"/>
       <c r="C36" s="1" t="n"/>
       <c r="D36" s="1" t="n"/>
@@ -2374,61 +2415,53 @@
       <c r="E37" s="1" t="n"/>
       <c r="F37" s="1" t="n"/>
     </row>
-    <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="29" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="1" t="n"/>
+      <c r="B38" s="1" t="n"/>
+      <c r="C38" s="1" t="n"/>
+      <c r="D38" s="1" t="n"/>
+      <c r="E38" s="1" t="n"/>
+      <c r="F38" s="1" t="n"/>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="29" t="inlineStr">
         <is>
           <t>4. 範圍</t>
         </is>
       </c>
-      <c r="B38" s="30" t="n"/>
-      <c r="C38" s="30" t="n"/>
-      <c r="D38" s="30" t="n"/>
-      <c r="E38" s="30" t="n"/>
-      <c r="F38" s="30" t="n"/>
-    </row>
-    <row r="39" ht="32" customHeight="1">
-      <c r="A39" s="13" t="inlineStr">
+      <c r="B39" s="30" t="n"/>
+      <c r="C39" s="30" t="n"/>
+      <c r="D39" s="30" t="n"/>
+      <c r="E39" s="30" t="n"/>
+      <c r="F39" s="30" t="n"/>
+    </row>
+    <row r="40" ht="32" customHeight="1">
+      <c r="A40" s="13" t="inlineStr">
         <is>
           <t>範圍內（In Scope）</t>
         </is>
       </c>
-      <c r="B39" s="32" t="n"/>
-      <c r="C39" s="33" t="n"/>
-      <c r="D39" s="13" t="inlineStr">
+      <c r="B40" s="32" t="n"/>
+      <c r="C40" s="33" t="n"/>
+      <c r="D40" s="13" t="inlineStr">
         <is>
           <t>不做什麼（Out of Scope）</t>
         </is>
       </c>
-      <c r="E39" s="32" t="n"/>
-      <c r="F39" s="33" t="n"/>
-    </row>
-    <row r="40" ht="30" customHeight="1">
-      <c r="A40" s="15" t="inlineStr">
-        <is>
-          <t>・僅限封裝段「晶粒外觀檢查站」；試行階段僅一條產線、一台取像站</t>
-        </is>
-      </c>
-      <c r="B40" s="31" t="n"/>
-      <c r="C40" s="31" t="n"/>
-      <c r="D40" s="15" t="inlineStr">
-        <is>
-          <t>✕ 不取代既有 AOI 機台或 Die Sorter；不改機台程式</t>
-        </is>
-      </c>
-      <c r="E40" s="31" t="n"/>
-      <c r="F40" s="31" t="n"/>
+      <c r="E40" s="32" t="n"/>
+      <c r="F40" s="33" t="n"/>
     </row>
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="15" t="inlineStr">
         <is>
-          <t>・缺陷分類依檢驗規範：CHP 崩角、CRK 裂紋、SCR 刮傷、CON 污染（後續版本可擴充）</t>
+          <t>・僅限封裝段「晶粒外觀檢查站」；試行階段僅一條產線、一台取像站</t>
         </is>
       </c>
       <c r="B41" s="31" t="n"/>
       <c r="C41" s="31" t="n"/>
       <c r="D41" s="15" t="inlineStr">
         <is>
-          <t>✕ 不擴及其他站點（晶圓前段、Bump、Wire bond、成品外觀）</t>
+          <t>✕ 不取代既有 AOI 機台或 Die Sorter；不改機台程式</t>
         </is>
       </c>
       <c r="E41" s="31" t="n"/>
@@ -2437,14 +2470,14 @@
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="15" t="inlineStr">
         <is>
-          <t>・AI 僅辨識缺陷分類、尺寸與檢驗區域；判定由系統依允收標準推導並記錄規範版本（ADR-0001）</t>
+          <t>・缺陷分類依檢驗規範：CHP 崩角、CRK 裂紋、SCR 刮傷、CON 污染（後續版本可擴充）</t>
         </is>
       </c>
       <c r="B42" s="31" t="n"/>
       <c r="C42" s="31" t="n"/>
       <c r="D42" s="15" t="inlineStr">
         <is>
-          <t>✕ 不由 AI 直接給出判定，不讓 AI 自動放行或退件</t>
+          <t>✕ 不擴及其他站點（晶圓前段、Bump、Wire bond、成品外觀）</t>
         </is>
       </c>
       <c r="E42" s="31" t="n"/>
@@ -2453,14 +2486,14 @@
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="15" t="inlineStr">
         <is>
-          <t>・判定 Warning 送人工複判之流程與紀錄</t>
+          <t>・AI 僅辨識缺陷分類、尺寸與檢驗區域；判定由系統依允收標準推導並記錄規範版本（ADR-0001）</t>
         </is>
       </c>
       <c r="B43" s="31" t="n"/>
       <c r="C43" s="31" t="n"/>
       <c r="D43" s="15" t="inlineStr">
         <is>
-          <t>✕ 不自行訓練／標註深度學習模型（若 ③ 結果需要，另案評估）</t>
+          <t>✕ 不由 AI 直接給出判定，不讓 AI 自動放行或退件</t>
         </is>
       </c>
       <c r="E43" s="31" t="n"/>
@@ -2469,14 +2502,14 @@
     <row r="44" ht="30" customHeight="1">
       <c r="A44" s="15" t="inlineStr">
         <is>
-          <t>・批不良率 p 管制圖、判異規則預警、AI 草擬異常處置單（經人確認後送出）</t>
+          <t>・判定 Warning 送人工複判之流程與紀錄</t>
         </is>
       </c>
       <c r="B44" s="31" t="n"/>
       <c r="C44" s="31" t="n"/>
       <c r="D44" s="15" t="inlineStr">
         <is>
-          <t>✕ 不修改客戶出貨規格；檢驗規範僅能等於或嚴於客戶規格</t>
+          <t>✕ 不自行訓練／標註深度學習模型（若 ③ 結果需要，另案評估）</t>
         </is>
       </c>
       <c r="E44" s="31" t="n"/>
@@ -2485,100 +2518,96 @@
     <row r="45" ht="30" customHeight="1">
       <c r="A45" s="15" t="inlineStr">
         <is>
-          <t>・④ 階段：判定結果、缺陷代碼、規範版本與批號上拋 MES</t>
+          <t>・批不良率 p 管制圖、判異規則預警、AI 草擬異常處置單（經人確認後送出）</t>
         </is>
       </c>
       <c r="B45" s="31" t="n"/>
       <c r="C45" s="31" t="n"/>
       <c r="D45" s="15" t="inlineStr">
         <is>
-          <t>✕ 不由系統自動 Hold 批（MES Hold 仍由人依異常處置單執行）</t>
+          <t>✕ 不修改客戶出貨規格；檢驗規範僅能等於或嚴於客戶規格</t>
         </is>
       </c>
       <c r="E45" s="31" t="n"/>
       <c r="F45" s="31" t="n"/>
     </row>
     <row r="46" ht="30" customHeight="1">
-      <c r="A46" s="15" t="n"/>
+      <c r="A46" s="15" t="inlineStr">
+        <is>
+          <t>・④ 階段：判定結果、缺陷代碼、規範版本與批號上拋 MES</t>
+        </is>
+      </c>
       <c r="B46" s="31" t="n"/>
       <c r="C46" s="31" t="n"/>
       <c r="D46" s="15" t="inlineStr">
         <is>
-          <t>✕ 不作為作業員績效考核依據</t>
+          <t>✕ 不由系統自動 Hold 批（MES Hold 仍由人依異常處置單執行）</t>
         </is>
       </c>
       <c r="E46" s="31" t="n"/>
       <c r="F46" s="31" t="n"/>
     </row>
-    <row r="47">
-      <c r="A47" s="1" t="n"/>
-      <c r="B47" s="1" t="n"/>
-      <c r="C47" s="1" t="n"/>
-      <c r="D47" s="1" t="n"/>
-      <c r="E47" s="1" t="n"/>
-      <c r="F47" s="1" t="n"/>
-    </row>
-    <row r="48" ht="22" customHeight="1">
-      <c r="A48" s="29" t="inlineStr">
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="15" t="n"/>
+      <c r="B47" s="31" t="n"/>
+      <c r="C47" s="31" t="n"/>
+      <c r="D47" s="15" t="inlineStr">
+        <is>
+          <t>✕ 不作為作業員績效考核依據</t>
+        </is>
+      </c>
+      <c r="E47" s="31" t="n"/>
+      <c r="F47" s="31" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n"/>
+      <c r="B48" s="1" t="n"/>
+      <c r="C48" s="1" t="n"/>
+      <c r="D48" s="1" t="n"/>
+      <c r="E48" s="1" t="n"/>
+      <c r="F48" s="1" t="n"/>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="29" t="inlineStr">
         <is>
           <t>5. 主要假設與限制</t>
         </is>
       </c>
-      <c r="B48" s="30" t="n"/>
-      <c r="C48" s="30" t="n"/>
-      <c r="D48" s="30" t="n"/>
-      <c r="E48" s="30" t="n"/>
-      <c r="F48" s="30" t="n"/>
-    </row>
-    <row r="49" ht="32" customHeight="1">
-      <c r="A49" s="13" t="inlineStr">
+      <c r="B49" s="30" t="n"/>
+      <c r="C49" s="30" t="n"/>
+      <c r="D49" s="30" t="n"/>
+      <c r="E49" s="30" t="n"/>
+      <c r="F49" s="30" t="n"/>
+    </row>
+    <row r="50" ht="32" customHeight="1">
+      <c r="A50" s="13" t="inlineStr">
         <is>
           <t>編號</t>
         </is>
       </c>
-      <c r="B49" s="13" t="inlineStr">
+      <c r="B50" s="13" t="inlineStr">
         <is>
           <t>假設內容</t>
         </is>
       </c>
-      <c r="C49" s="32" t="n"/>
-      <c r="D49" s="32" t="n"/>
-      <c r="E49" s="33" t="n"/>
-      <c r="F49" s="13" t="inlineStr">
+      <c r="C50" s="32" t="n"/>
+      <c r="D50" s="32" t="n"/>
+      <c r="E50" s="33" t="n"/>
+      <c r="F50" s="13" t="inlineStr">
         <is>
           <t>驗證時點</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="30" customHeight="1">
-      <c r="A50" s="36" t="inlineStr">
-        <is>
-          <t>A1</t>
-        </is>
-      </c>
-      <c r="B50" s="15" t="inlineStr">
-        <is>
-          <t>試行線可加裝固定光源治具與取像站，影像解析度可達 5 µm/px（檢驗規範 v1 換算基準）</t>
-        </is>
-      </c>
-      <c r="C50" s="31" t="n"/>
-      <c r="D50" s="31" t="n"/>
-      <c r="E50" s="31" t="n"/>
-      <c r="F50" s="26" t="inlineStr">
-        <is>
-          <t>W3 取像條件定義</t>
         </is>
       </c>
     </row>
     <row r="51" ht="30" customHeight="1">
       <c r="A51" s="36" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="B51" s="15" t="inlineStr">
         <is>
-          <t>QA 可自產線挑選標準樣本並經量測確認標準答案；稀少缺陷（如 CRK）收集期可能延長</t>
+          <t>試行線可加裝固定光源治具與取像站，影像解析度可達 5 µm/px（檢驗規範 v1 換算基準）</t>
         </is>
       </c>
       <c r="C51" s="31" t="n"/>
@@ -2586,19 +2615,19 @@
       <c r="E51" s="31" t="n"/>
       <c r="F51" s="26" t="inlineStr">
         <is>
-          <t>W4 樣本收集</t>
+          <t>W3 取像條件定義</t>
         </is>
       </c>
     </row>
     <row r="52" ht="30" customHeight="1">
       <c r="A52" s="36" t="inlineStr">
         <is>
-          <t>A3</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="B52" s="15" t="inlineStr">
         <is>
-          <t>資安單位核可影像送外部 AI 服務（去識別化後）或核撥地端方案預算</t>
+          <t>QA 可自產線挑選標準樣本並經量測確認標準答案；稀少缺陷（如 CRK）收集期可能延長</t>
         </is>
       </c>
       <c r="C52" s="31" t="n"/>
@@ -2606,19 +2635,19 @@
       <c r="E52" s="31" t="n"/>
       <c r="F52" s="26" t="inlineStr">
         <is>
-          <t>W5 資安評估</t>
+          <t>W4 樣本收集</t>
         </is>
       </c>
     </row>
     <row r="53" ht="30" customHeight="1">
       <c r="A53" s="36" t="inlineStr">
         <is>
-          <t>A4</t>
+          <t>A3</t>
         </is>
       </c>
       <c r="B53" s="15" t="inlineStr">
         <is>
-          <t>③ 試行期間人工目檢照常執行，AI 判定不影響放行，僅作並行比對</t>
+          <t>資安單位核可影像送外部 AI 服務（去識別化後）或核撥地端方案預算</t>
         </is>
       </c>
       <c r="C53" s="31" t="n"/>
@@ -2626,19 +2655,19 @@
       <c r="E53" s="31" t="n"/>
       <c r="F53" s="26" t="inlineStr">
         <is>
-          <t>W19 試行啟動</t>
+          <t>W5 資安評估</t>
         </is>
       </c>
     </row>
     <row r="54" ht="30" customHeight="1">
       <c r="A54" s="36" t="inlineStr">
         <is>
-          <t>A5</t>
+          <t>A4</t>
         </is>
       </c>
       <c r="B54" s="15" t="inlineStr">
         <is>
-          <t>IT/MES 於第 19 週起可投入介接規格與開發資源（約 7 週）</t>
+          <t>③ 試行期間人工目檢照常執行，AI 判定不影響放行，僅作並行比對</t>
         </is>
       </c>
       <c r="C54" s="31" t="n"/>
@@ -2646,19 +2675,19 @@
       <c r="E54" s="31" t="n"/>
       <c r="F54" s="26" t="inlineStr">
         <is>
-          <t>W19 介接規格</t>
+          <t>W19 試行啟動</t>
         </is>
       </c>
     </row>
     <row r="55" ht="30" customHeight="1">
       <c r="A55" s="36" t="inlineStr">
         <is>
-          <t>A6</t>
+          <t>A5</t>
         </is>
       </c>
       <c r="B55" s="15" t="inlineStr">
         <is>
-          <t>PoC 之一致性分析以半合成樣本與模擬評估者完成（ADR-0002）；實際導入須以產線樣本與真人作業員重做</t>
+          <t>IT/MES 於第 19 週起可投入介接規格與開發資源（約 7 週）</t>
         </is>
       </c>
       <c r="C55" s="31" t="n"/>
@@ -2666,19 +2695,19 @@
       <c r="E55" s="31" t="n"/>
       <c r="F55" s="26" t="inlineStr">
         <is>
-          <t>① 階段 MSA</t>
+          <t>W19 介接規格</t>
         </is>
       </c>
     </row>
     <row r="56" ht="30" customHeight="1">
       <c r="A56" s="36" t="inlineStr">
         <is>
-          <t>A7</t>
+          <t>A6</t>
         </is>
       </c>
       <c r="B56" s="15" t="inlineStr">
         <is>
-          <t>規範 v2 重跑之 API 預算可獲核准（v2 已於作品中重跑：實際 US$9.55／240 次呼叫，原估 US$3–4 低估；v1 第 2 次判定補跑 US$1.17）</t>
+          <t>PoC 之一致性分析以半合成樣本與模擬評估者完成（ADR-0002）；實際導入須以產線樣本與真人作業員重做</t>
         </is>
       </c>
       <c r="C56" s="31" t="n"/>
@@ -2686,180 +2715,176 @@
       <c r="E56" s="31" t="n"/>
       <c r="F56" s="26" t="inlineStr">
         <is>
+          <t>① 階段 MSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="30" customHeight="1">
+      <c r="A57" s="36" t="inlineStr">
+        <is>
+          <t>A7</t>
+        </is>
+      </c>
+      <c r="B57" s="15" t="inlineStr">
+        <is>
+          <t>規範 v2 重跑之 API 預算可獲核准（v2 已於作品中重跑：實際 US$9.55／240 次呼叫，原估 US$3–4 低估；v1 第 2 次判定補跑 US$1.17）</t>
+        </is>
+      </c>
+      <c r="C57" s="31" t="n"/>
+      <c r="D57" s="31" t="n"/>
+      <c r="E57" s="31" t="n"/>
+      <c r="F57" s="26" t="inlineStr">
+        <is>
           <t>W14 預算核准</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="1" t="n"/>
-      <c r="B57" s="1" t="n"/>
-      <c r="C57" s="1" t="n"/>
-      <c r="D57" s="1" t="n"/>
-      <c r="E57" s="1" t="n"/>
-      <c r="F57" s="1" t="n"/>
-    </row>
-    <row r="58" ht="22" customHeight="1">
-      <c r="A58" s="29" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="1" t="n"/>
+      <c r="B58" s="1" t="n"/>
+      <c r="C58" s="1" t="n"/>
+      <c r="D58" s="1" t="n"/>
+      <c r="E58" s="1" t="n"/>
+      <c r="F58" s="1" t="n"/>
+    </row>
+    <row r="59" ht="22" customHeight="1">
+      <c r="A59" s="29" t="inlineStr">
         <is>
           <t>6. 專案成員與角色</t>
         </is>
       </c>
-      <c r="B58" s="30" t="n"/>
-      <c r="C58" s="30" t="n"/>
-      <c r="D58" s="30" t="n"/>
-      <c r="E58" s="30" t="n"/>
-      <c r="F58" s="30" t="n"/>
-    </row>
-    <row r="59" ht="32" customHeight="1">
-      <c r="A59" s="13" t="inlineStr">
+      <c r="B59" s="30" t="n"/>
+      <c r="C59" s="30" t="n"/>
+      <c r="D59" s="30" t="n"/>
+      <c r="E59" s="30" t="n"/>
+      <c r="F59" s="30" t="n"/>
+    </row>
+    <row r="60" ht="32" customHeight="1">
+      <c r="A60" s="13" t="inlineStr">
         <is>
           <t>角色</t>
         </is>
       </c>
-      <c r="B59" s="13" t="inlineStr">
+      <c r="B60" s="13" t="inlineStr">
         <is>
           <t>單位</t>
         </is>
       </c>
-      <c r="C59" s="13" t="inlineStr">
+      <c r="C60" s="13" t="inlineStr">
         <is>
           <t>主要職責</t>
         </is>
       </c>
-      <c r="D59" s="33" t="n"/>
-      <c r="E59" s="13" t="inlineStr">
+      <c r="D60" s="33" t="n"/>
+      <c r="E60" s="13" t="inlineStr">
         <is>
           <t>投入比例（預估）</t>
         </is>
       </c>
-      <c r="F59" s="13" t="inlineStr">
+      <c r="F60" s="13" t="inlineStr">
         <is>
           <t>備註</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="30" customHeight="1">
-      <c r="A60" s="34" t="inlineStr">
-        <is>
-          <t>專案發起人</t>
-        </is>
-      </c>
-      <c r="B60" s="26" t="inlineStr">
-        <is>
-          <t>製造處</t>
-        </is>
-      </c>
-      <c r="C60" s="15" t="inlineStr">
-        <is>
-          <t>核定章程與資源、Gate 審查最終簽核、跨部門議題裁決</t>
-        </is>
-      </c>
-      <c r="D60" s="31" t="n"/>
-      <c r="E60" s="26" t="inlineStr">
-        <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="F60" s="15" t="inlineStr">
-        <is>
-          <t>跨部門主管會議主席</t>
         </is>
       </c>
     </row>
     <row r="61" ht="30" customHeight="1">
       <c r="A61" s="34" t="inlineStr">
         <is>
-          <t>專案經理（專案專員）</t>
+          <t>專案發起人</t>
         </is>
       </c>
       <c r="B61" s="26" t="inlineStr">
         <is>
-          <t>智慧製造</t>
+          <t>製造處</t>
         </is>
       </c>
       <c r="C61" s="15" t="inlineStr">
         <is>
-          <t>時程與週會追蹤、PoC 建置、一致性分析、風險與升級管理</t>
+          <t>核定章程與資源、Gate 審查最終簽核、跨部門議題裁決</t>
         </is>
       </c>
       <c r="D61" s="31" t="n"/>
       <c r="E61" s="26" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="F61" s="15" t="inlineStr">
         <is>
-          <t>本文件撰寫人</t>
+          <t>跨部門主管會議主席</t>
         </is>
       </c>
     </row>
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="34" t="inlineStr">
         <is>
-          <t>品質代表</t>
+          <t>專案經理（專案專員）</t>
         </is>
       </c>
       <c r="B62" s="26" t="inlineStr">
         <is>
-          <t>QA/品保</t>
+          <t>智慧製造</t>
         </is>
       </c>
       <c r="C62" s="15" t="inlineStr">
         <is>
-          <t>標準樣本與標準答案、檢驗規範審查與發行、漏判風險把關</t>
+          <t>時程與週會追蹤、PoC 建置、一致性分析、風險與升級管理</t>
         </is>
       </c>
       <c r="D62" s="31" t="n"/>
       <c r="E62" s="26" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="F62" s="15" t="inlineStr">
         <is>
-          <t>規範 Owner</t>
+          <t>本文件撰寫人</t>
         </is>
       </c>
     </row>
     <row r="63" ht="30" customHeight="1">
       <c r="A63" s="34" t="inlineStr">
         <is>
-          <t>製程代表</t>
+          <t>品質代表</t>
         </is>
       </c>
       <c r="B63" s="26" t="inlineStr">
         <is>
-          <t>製程工程</t>
+          <t>QA/品保</t>
         </is>
       </c>
       <c r="C63" s="15" t="inlineStr">
         <is>
-          <t>允收標準技術依據、p 管制圖判異規則、異常處置單內容</t>
+          <t>標準樣本與標準答案、檢驗規範審查與發行、漏判風險把關</t>
         </is>
       </c>
       <c r="D63" s="31" t="n"/>
       <c r="E63" s="26" t="inlineStr">
         <is>
-          <t>20%</t>
-        </is>
-      </c>
-      <c r="F63" s="15" t="inlineStr"/>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="F63" s="15" t="inlineStr">
+        <is>
+          <t>規範 Owner</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="30" customHeight="1">
       <c r="A64" s="34" t="inlineStr">
         <is>
-          <t>設備代表</t>
+          <t>製程代表</t>
         </is>
       </c>
       <c r="B64" s="26" t="inlineStr">
         <is>
-          <t>設備工程</t>
+          <t>製程工程</t>
         </is>
       </c>
       <c r="C64" s="15" t="inlineStr">
         <is>
-          <t>光源治具與取像站、µm/px 校正、機台差異驗證</t>
+          <t>允收標準技術依據、p 管制圖判異規則、異常處置單內容</t>
         </is>
       </c>
       <c r="D64" s="31" t="n"/>
@@ -2868,161 +2893,169 @@
           <t>20%</t>
         </is>
       </c>
-      <c r="F64" s="15" t="inlineStr">
-        <is>
-          <t>治具請購協同採購</t>
-        </is>
-      </c>
+      <c r="F64" s="15" t="inlineStr"/>
     </row>
     <row r="65" ht="30" customHeight="1">
       <c r="A65" s="34" t="inlineStr">
         <is>
-          <t>系統代表</t>
+          <t>設備代表</t>
         </is>
       </c>
       <c r="B65" s="26" t="inlineStr">
         <is>
-          <t>IT/MES</t>
+          <t>設備工程</t>
         </is>
       </c>
       <c r="C65" s="15" t="inlineStr">
         <is>
-          <t>資安評估、PoC 環境、MES 介接開發與上線</t>
+          <t>光源治具與取像站、µm/px 校正、機台差異驗證</t>
         </is>
       </c>
       <c r="D65" s="31" t="n"/>
       <c r="E65" s="26" t="inlineStr">
         <is>
-          <t>20%（④ 階段 50%）</t>
-        </is>
-      </c>
-      <c r="F65" s="15" t="inlineStr"/>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="F65" s="15" t="inlineStr">
+        <is>
+          <t>治具請購協同採購</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="30" customHeight="1">
       <c r="A66" s="34" t="inlineStr">
         <is>
-          <t>產線代表</t>
+          <t>系統代表</t>
         </is>
       </c>
       <c r="B66" s="26" t="inlineStr">
         <is>
-          <t>生產/製造</t>
+          <t>IT/MES</t>
         </is>
       </c>
       <c r="C66" s="15" t="inlineStr">
         <is>
-          <t>目檢站作業員調度、並行比對執行、人工複判紀錄</t>
+          <t>資安評估、PoC 環境、MES 介接開發與上線</t>
         </is>
       </c>
       <c r="D66" s="31" t="n"/>
       <c r="E66" s="26" t="inlineStr">
         <is>
-          <t>15%</t>
-        </is>
-      </c>
-      <c r="F66" s="15" t="inlineStr">
-        <is>
-          <t>目檢站班長</t>
-        </is>
-      </c>
+          <t>20%（④ 階段 50%）</t>
+        </is>
+      </c>
+      <c r="F66" s="15" t="inlineStr"/>
     </row>
     <row r="67" ht="30" customHeight="1">
       <c r="A67" s="34" t="inlineStr">
         <is>
-          <t>生管代表</t>
+          <t>產線代表</t>
         </is>
       </c>
       <c r="B67" s="26" t="inlineStr">
         <is>
-          <t>生管</t>
+          <t>生產/製造</t>
         </is>
       </c>
       <c r="C67" s="15" t="inlineStr">
         <is>
-          <t>試行期產能與人力影響評估、批排程配合</t>
+          <t>目檢站作業員調度、並行比對執行、人工複判紀錄</t>
         </is>
       </c>
       <c r="D67" s="31" t="n"/>
       <c r="E67" s="26" t="inlineStr">
         <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="F67" s="15" t="inlineStr">
+        <is>
+          <t>目檢站班長</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="30" customHeight="1">
+      <c r="A68" s="34" t="inlineStr">
+        <is>
+          <t>生管代表</t>
+        </is>
+      </c>
+      <c r="B68" s="26" t="inlineStr">
+        <is>
+          <t>生管</t>
+        </is>
+      </c>
+      <c r="C68" s="15" t="inlineStr">
+        <is>
+          <t>試行期產能與人力影響評估、批排程配合</t>
+        </is>
+      </c>
+      <c r="D68" s="31" t="n"/>
+      <c r="E68" s="26" t="inlineStr">
+        <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="F67" s="15" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="1" t="n"/>
-      <c r="B68" s="1" t="n"/>
-      <c r="C68" s="1" t="n"/>
-      <c r="D68" s="1" t="n"/>
-      <c r="E68" s="1" t="n"/>
-      <c r="F68" s="1" t="n"/>
-    </row>
-    <row r="69" ht="22" customHeight="1">
-      <c r="A69" s="29" t="inlineStr">
+      <c r="F68" s="15" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="n"/>
+      <c r="B69" s="1" t="n"/>
+      <c r="C69" s="1" t="n"/>
+      <c r="D69" s="1" t="n"/>
+      <c r="E69" s="1" t="n"/>
+      <c r="F69" s="1" t="n"/>
+    </row>
+    <row r="70" ht="22" customHeight="1">
+      <c r="A70" s="29" t="inlineStr">
         <is>
           <t>7. 簽核</t>
         </is>
       </c>
-      <c r="B69" s="30" t="n"/>
-      <c r="C69" s="30" t="n"/>
-      <c r="D69" s="30" t="n"/>
-      <c r="E69" s="30" t="n"/>
-      <c r="F69" s="30" t="n"/>
-    </row>
-    <row r="70" ht="32" customHeight="1">
-      <c r="A70" s="13" t="inlineStr">
+      <c r="B70" s="30" t="n"/>
+      <c r="C70" s="30" t="n"/>
+      <c r="D70" s="30" t="n"/>
+      <c r="E70" s="30" t="n"/>
+      <c r="F70" s="30" t="n"/>
+    </row>
+    <row r="71" ht="32" customHeight="1">
+      <c r="A71" s="13" t="inlineStr">
         <is>
           <t>簽核角色</t>
         </is>
       </c>
-      <c r="B70" s="13" t="inlineStr">
+      <c r="B71" s="13" t="inlineStr">
         <is>
           <t>單位</t>
         </is>
       </c>
-      <c r="C70" s="13" t="inlineStr">
+      <c r="C71" s="13" t="inlineStr">
         <is>
           <t>姓名</t>
         </is>
       </c>
-      <c r="D70" s="13" t="inlineStr">
+      <c r="D71" s="13" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="E70" s="13" t="inlineStr">
+      <c r="E71" s="13" t="inlineStr">
         <is>
           <t>意見</t>
         </is>
       </c>
-      <c r="F70" s="33" t="n"/>
-    </row>
-    <row r="71" ht="26" customHeight="1">
-      <c r="A71" s="34" t="inlineStr">
-        <is>
-          <t>專案發起人</t>
-        </is>
-      </c>
-      <c r="B71" s="26" t="inlineStr">
-        <is>
-          <t>製造處</t>
-        </is>
-      </c>
-      <c r="C71" s="15" t="n"/>
-      <c r="D71" s="15" t="n"/>
-      <c r="E71" s="15" t="n"/>
       <c r="F71" s="33" t="n"/>
     </row>
     <row r="72" ht="26" customHeight="1">
       <c r="A72" s="34" t="inlineStr">
         <is>
-          <t>品質主管</t>
+          <t>專案發起人</t>
         </is>
       </c>
       <c r="B72" s="26" t="inlineStr">
         <is>
-          <t>QA/品保</t>
+          <t>製造處</t>
         </is>
       </c>
       <c r="C72" s="15" t="n"/>
@@ -3033,12 +3066,12 @@
     <row r="73" ht="26" customHeight="1">
       <c r="A73" s="34" t="inlineStr">
         <is>
-          <t>專案經理</t>
+          <t>品質主管</t>
         </is>
       </c>
       <c r="B73" s="26" t="inlineStr">
         <is>
-          <t>智慧製造</t>
+          <t>QA/品保</t>
         </is>
       </c>
       <c r="C73" s="15" t="n"/>
@@ -3046,12 +3079,28 @@
       <c r="E73" s="15" t="n"/>
       <c r="F73" s="33" t="n"/>
     </row>
+    <row r="74" ht="26" customHeight="1">
+      <c r="A74" s="34" t="inlineStr">
+        <is>
+          <t>專案經理</t>
+        </is>
+      </c>
+      <c r="B74" s="26" t="inlineStr">
+        <is>
+          <t>智慧製造</t>
+        </is>
+      </c>
+      <c r="C74" s="15" t="n"/>
+      <c r="D74" s="15" t="n"/>
+      <c r="E74" s="15" t="n"/>
+      <c r="F74" s="33" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="55">
     <mergeCell ref="A41:C41"/>
     <mergeCell ref="B7:F7"/>
-    <mergeCell ref="B49:E49"/>
     <mergeCell ref="C62:D62"/>
+    <mergeCell ref="C68:D68"/>
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="D41:F41"/>
     <mergeCell ref="A46:C46"/>
@@ -3059,11 +3108,13 @@
     <mergeCell ref="B55:E55"/>
     <mergeCell ref="B51:E51"/>
     <mergeCell ref="C64:D64"/>
+    <mergeCell ref="D47:F47"/>
     <mergeCell ref="B18:F18"/>
     <mergeCell ref="D43:F43"/>
     <mergeCell ref="A33:F33"/>
     <mergeCell ref="A42:C42"/>
     <mergeCell ref="E73:F73"/>
+    <mergeCell ref="A47:C47"/>
     <mergeCell ref="B50:E50"/>
     <mergeCell ref="C63:D63"/>
     <mergeCell ref="C65:D65"/>
@@ -3072,11 +3123,10 @@
     <mergeCell ref="A35:F35"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B8:F8"/>
-    <mergeCell ref="D39:F39"/>
     <mergeCell ref="B17:F17"/>
     <mergeCell ref="A43:C43"/>
     <mergeCell ref="B13:F13"/>
-    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="E74:F74"/>
     <mergeCell ref="D42:F42"/>
     <mergeCell ref="B56:E56"/>
     <mergeCell ref="A44:C44"/>
@@ -3088,17 +3138,16 @@
     <mergeCell ref="C61:D61"/>
     <mergeCell ref="A34:F34"/>
     <mergeCell ref="D44:F44"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="A30:F30"/>
-    <mergeCell ref="E70:F70"/>
     <mergeCell ref="B9:F9"/>
+    <mergeCell ref="B57:E57"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="B53:E53"/>
+    <mergeCell ref="A36:F36"/>
     <mergeCell ref="A45:C45"/>
+    <mergeCell ref="B15:F15"/>
     <mergeCell ref="C67:D67"/>
-    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="D46:F46"/>
     <mergeCell ref="E72:F72"/>
-    <mergeCell ref="D46:F46"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="D40:F40"/>
     <mergeCell ref="C66:D66"/>
@@ -4094,7 +4143,7 @@
       </c>
       <c r="C10" s="15" t="inlineStr">
         <is>
-          <t>現況人工目檢一致性分析（3 位作業員 × 2 輪，口述標準）</t>
+          <t>現況人工判讀一致性分析（3 位檢驗員 × 2 輪，依現行規範）</t>
         </is>
       </c>
       <c r="D10" s="26" t="inlineStr">
@@ -4165,12 +4214,12 @@
       <c r="AR10" s="56" t="n"/>
       <c r="AS10" s="15" t="inlineStr">
         <is>
-          <t>Before 基準線。PoC 以模擬評估者示範：評估者間一致率 57.5%、漏判率 14.8%、人工複判率 42.5%、重複性 85.8%（實際導入須以作業員重測）</t>
+          <t>人工基準線。PoC 以作者本人照規範判兩輪示範（79 筆）：每顆 34.9 秒、漏判率 23.5%、對標準答案一致率 70.9%、重複性 87.2%、誤判率 2.3%（實際導入須以 3 位檢驗員重測）</t>
         </is>
       </c>
       <c r="AT10" s="57" t="inlineStr">
         <is>
-          <t>模擬示範（模擬評估者）</t>
+          <t>模擬示範（作者本人）</t>
         </is>
       </c>
     </row>

--- a/docs/rollout/導入計畫.xlsx
+++ b/docs/rollout/導入計畫.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="封面" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="專案章程" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="時程表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RACI" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="風險清單" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="週會追蹤表" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="封面" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="專案章程" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="時程表" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="RACI" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="風險清單" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="週會追蹤表" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'時程表'!$A$4:$K$41</definedName>
@@ -1261,7 +1261,7 @@
       <c r="B5" s="4" t="inlineStr">
         <is>
           <t>⚠ 本文件為「模擬情境」之導入計畫，非實際產線導入紀錄。
-・情境、數據與組織皆為假設；痛點來源為作者過去的目檢經驗（產線有檢驗規範，但判讀靠人眼）；人工基準線為作者本人照規範判兩輪（79 筆，真實）。
+・情境、數據與組織皆為假設；痛點來源為作者過去在產線看到的狀況（產線有檢驗規範，但判讀靠人眼）；人工基準線為作者本人照規範判兩輪（79 筆，真實）。
 ・導入階段 ② PoC 已於模擬情境以檢驗規範 v1 執行（40 張半合成影像、3 位模擬 AI 評估者）：結果「未通過」Gate ②→③（漏判率 37.0%，目標 ≤ 5%；改善後重複性 77.5%，目標 ≥ 90%）。
 ・規範 v2 已於作品中重跑一次（2026-10-07，同樣本、同評估者、240 筆）：漏判率 0%、重複性 92.5%、人工複判率 25.8% 達標；評估者間一致率 82.5%、誤判率 7.6% 未達，預警提早尚未以 v2 重驗 → Gate ②→③（v2）尚未通過。③ 單線試行、④ 擴線與 MES 介接仍為「規劃」。數據出處：experiment/results/msa-summary.md</t>
         </is>

--- a/docs/rollout/導入計畫.xlsx
+++ b/docs/rollout/導入計畫.xlsx
@@ -1215,7 +1215,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1263,7 +1263,8 @@
           <t>⚠ 本文件為「模擬情境」之導入計畫，非實際產線導入紀錄。
 ・情境、數據與組織皆為假設；痛點來源為作者過去在產線看到的狀況（產線有檢驗規範，但判讀靠人眼）；人工基準線為作者本人照規範判兩輪（79 筆，真實）。
 ・導入階段 ② PoC 已於模擬情境以檢驗規範 v1 執行（40 張半合成影像、3 位模擬 AI 評估者）：結果「未通過」Gate ②→③（漏判率 37.0%，目標 ≤ 5%；改善後重複性 77.5%，目標 ≥ 90%）。
-・規範 v2 已於作品中重跑一次（2026-10-07，同樣本、同評估者、240 筆）：漏判率 0%、重複性 92.5%、人工複判率 25.8% 達標；評估者間一致率 82.5%、誤判率 7.6% 未達，預警提早尚未以 v2 重驗 → Gate ②→③（v2）尚未通過。③ 單線試行、④ 擴線與 MES 介接仍為「規劃」。數據出處：experiment/results/msa-summary.md</t>
+・規範 v2 已於作品中重跑一次（2026-10-07，同樣本、同評估者、240 筆）：漏判率 0%、重複性 92.5%、人工複判率 25.8% 達標；評估者間一致率 82.5%、誤判率 7.6% 未達，預警提早尚未以 v2 重驗 → Gate ②→③（v2）尚未通過。
+・規範 v2.1（只改量測）於 2026-10-13 凍結（tag spec-v2.1-frozen）後，以凍結 commit 雜湊為種子產生 40 張盲測集重跑（240 筆、US$9.53）：答對率 92.5%、漏判率 0%、誤判率 0%、人工複判率 26.7%、重複性 93.3% 達標；評估者間一致率 87.5% 未達 → Gate ②→③（v2.1）差一項，仍未通過。③ 單線試行、④ 擴線與 MES 介接仍為「規劃」。數據出處：experiment/results/msa-summary.md</t>
         </is>
       </c>
       <c r="C5" s="5" t="n"/>
@@ -1324,7 +1325,7 @@
       </c>
       <c r="C11" s="15" t="inlineStr">
         <is>
-          <t>v0.5（草案）</t>
+          <t>v0.6（草案）</t>
         </is>
       </c>
       <c r="D11" s="1" t="n"/>
@@ -1448,12 +1449,12 @@
       </c>
       <c r="C20" s="15" t="inlineStr">
         <is>
-          <t>AI 辨識缺陷分類＋規則推導判定；一致性分析、p 管制圖預警。v1 漏判率 37.0%（CHP 偵出率 14.8%、CRK 0%、尺寸系統偏差）→ 規範 v2 重跑：漏判率 0%、重複性 92.5%，但誤判率 7.6%</t>
+          <t>AI 辨識缺陷分類＋規則推導判定；一致性分析、p 管制圖預警。v1 漏判率 37.0%（CHP 偵出率 14.8%、CRK 0%、尺寸系統偏差）→ 規範 v2 重跑：漏判率 0%、重複性 92.5%，但誤判率 7.6% → 規範 v2.1 凍結後盲測：誤判率 0%、答對率 92.5%，評估者間一致率 87.5%</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>v1 未通過 Gate；v2 已重跑・Gate 未通過</t>
+          <t>v1、v2 未通過；v2.1 盲測差一項・Gate 未通過</t>
         </is>
       </c>
     </row>
@@ -1684,6 +1685,22 @@
       <c r="D36" s="26" t="inlineStr">
         <is>
           <t>v0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="1" t="n"/>
+      <c r="B37" s="25" t="n">
+        <v>46309</v>
+      </c>
+      <c r="C37" s="15" t="inlineStr">
+        <is>
+          <t>回填第三輪：規範 v2.1（只改量測）凍結後以盲測集重跑（240 次、US$9.53），五項 KPI 達標、評估者間一致率 87.5% 未達；人工基準線改為作者盲測兩輪（隔天，每顆 46.7 秒）</t>
+        </is>
+      </c>
+      <c r="D37" s="26" t="inlineStr">
+        <is>
+          <t>v0.6</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1930,7 @@
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>產線有檢驗規範，但每顆都要人眼找缺陷、量尺寸、對條文；作者照規範實測每顆 34.9 秒，檢驗站產能受限於人力。</t>
+          <t>產線有檢驗規範，但每顆都要人眼找缺陷、量尺寸、對條文；作者照規範盲測實測每顆 46.7 秒，檢驗站產能受限於人力。</t>
         </is>
       </c>
       <c r="C14" s="31" t="n"/>
@@ -2019,13 +2036,13 @@
       <c r="C21" s="13" t="inlineStr">
         <is>
           <t>基準線
-（人眼＋規範：作者實測）</t>
+（人眼＋規範：作者盲測）</t>
         </is>
       </c>
       <c r="D21" s="13" t="inlineStr">
         <is>
           <t>PoC 實測
-（規範 v1 → v2）</t>
+（v1 → v2 → v2.1 盲測）</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
@@ -2052,13 +2069,13 @@
       </c>
       <c r="C22" s="26" t="inlineStr">
         <is>
-          <t>34.9 秒（作者實測）</t>
+          <t>46.7 秒（作者盲測實測）</t>
         </is>
       </c>
       <c r="D22" s="35" t="inlineStr">
         <is>
-          <t>v2：8.2 秒
-比人工快約 4 倍</t>
+          <t>v2：8.2 秒 → v2.1：8.9 秒
+比人工快約 5 倍</t>
         </is>
       </c>
       <c r="E22" s="36" t="inlineStr">
@@ -2085,13 +2102,13 @@
       </c>
       <c r="C23" s="26" t="inlineStr">
         <is>
-          <t>23.5%（4/17）</t>
+          <t>22.2%（4/18）</t>
         </is>
       </c>
       <c r="D23" s="35" t="inlineStr">
         <is>
-          <t>37.0% → 0.0%（0/27）
-v2 達標</t>
+          <t>37.0% → 0.0% → 0.0%（0/27）
+v2.1 達標</t>
         </is>
       </c>
       <c r="E23" s="36" t="inlineStr">
@@ -2118,13 +2135,13 @@
       </c>
       <c r="C24" s="26" t="inlineStr">
         <is>
-          <t>87.2%（39 組配對）</t>
+          <t>67.5%（40 組，隔天重判）</t>
         </is>
       </c>
       <c r="D24" s="35" t="inlineStr">
         <is>
-          <t>77.5% → 92.5%（120 組配對）
-v2 達標</t>
+          <t>77.5% → 92.5% → 93.3%（120 組配對）
+v2.1 達標</t>
         </is>
       </c>
       <c r="E24" s="36" t="inlineStr">
@@ -2151,13 +2168,13 @@
       </c>
       <c r="C25" s="26" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="D25" s="35" t="inlineStr">
         <is>
-          <t>23.3% → 25.8%（標準答案 22.5%）
-v2 達標</t>
+          <t>23.3% → 25.8% → 26.7%（標準答案 22.5%）
+v2.1 達標</t>
         </is>
       </c>
       <c r="E25" s="36" t="inlineStr">
@@ -2189,8 +2206,8 @@
       </c>
       <c r="D26" s="37" t="inlineStr">
         <is>
-          <t>60.0% → 82.5%
-v2 未達標</t>
+          <t>60.0% → 82.5% → 87.5%（35/40）
+v2.1 未達標</t>
         </is>
       </c>
       <c r="E26" s="36" t="inlineStr">
@@ -2217,13 +2234,13 @@
       </c>
       <c r="C27" s="26" t="inlineStr">
         <is>
-          <t>70.9%</t>
-        </is>
-      </c>
-      <c r="D27" s="37" t="inlineStr">
-        <is>
-          <t>60.8% → 75.8%
-v2 未達標</t>
+          <t>77.5%</t>
+        </is>
+      </c>
+      <c r="D27" s="35" t="inlineStr">
+        <is>
+          <t>60.8% → 75.8% → 92.5%
+v2.1 達標</t>
         </is>
       </c>
       <c r="E27" s="36" t="inlineStr">
@@ -2250,13 +2267,13 @@
       </c>
       <c r="C28" s="26" t="inlineStr">
         <is>
-          <t>2.3%（1/43）</t>
-        </is>
-      </c>
-      <c r="D28" s="37" t="inlineStr">
-        <is>
-          <t>3.0% → 7.6%（5/66）
-v2 未達標</t>
+          <t>2.3%（1/44）</t>
+        </is>
+      </c>
+      <c r="D28" s="35" t="inlineStr">
+        <is>
+          <t>3.0% → 7.6% → 0.0%（0/66）
+v2.1 達標</t>
         </is>
       </c>
       <c r="E28" s="36" t="inlineStr">
@@ -2289,7 +2306,7 @@
       <c r="D29" s="37" t="inlineStr">
         <is>
           <t>v1：0 批（L24 預警＝異常；完美判定亦未提早）
-v2：尚未重新驗證</t>
+v2、v2.1：尚未重新驗證</t>
         </is>
       </c>
       <c r="E29" s="36" t="inlineStr">
@@ -2338,7 +2355,7 @@
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="38" t="inlineStr">
         <is>
-          <t>判讀（照實）：規範 v1 的 AI 漏判率 37.0%，比人工 23.5% 還高，② Gate（v1）未通過；規範 v2 重跑後 AI 每顆 8.2 秒（人工 34.9 秒）、漏判率 0%、重複性 92.5%、人工複判率 25.8% 達標，但評估者間一致率 82.5%、誤判率 7.6%（人工 2.3%）未達，預警提早尚未重驗 → Gate（v2）尚未通過。</t>
+          <t>判讀（照實）：規範 v1 的 AI 漏判率 37.0%，比人工 23.5% 還高，② Gate（v1）未通過；規範 v2 重跑後 AI 每顆 8.2 秒（人工 34.9 秒）、漏判率 0%、重複性 92.5%、人工複判率 25.8% 達標，但評估者間一致率 82.5%、誤判率 7.6%（人工 2.3%）未達。規範 v2.1 凍結後在盲測集：AI 每顆 8.9 秒（人工 46.7 秒）、答對率 92.5%（人工 77.5%）、漏判 0%（人工 22.2%）、誤判 0%（人工 2.3%），評估者間一致率 87.5% 仍未達，預警提早尚未重驗 → Gate（v2.1）差一項、尚未通過。</t>
         </is>
       </c>
       <c r="B31" s="1" t="n"/>
@@ -2350,7 +2367,7 @@
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="39" t="inlineStr">
         <is>
-          <t>・基準線為作者本人照規範判兩輪（79 筆，真實），只有一人且為規範撰寫者；試行期須以 3 位檢驗員重測。另一對照：只給 AI 口述標準時評估者間一致率 57.5%、人工複判率 42.5%，說明 AI 必須搭配規則。</t>
+          <t>・基準線為作者本人照規範判盲測集兩輪（80 筆、分在不同天，真實；開發集同日兩輪的重複性 87.2% 有記憶效應），只有一人且為規範撰寫者；試行期須以 3 位檢驗員重測。另一對照：只給 AI 口述標準時評估者間一致率 57.5%、人工複判率 42.5%，說明 AI 必須搭配規則。</t>
         </is>
       </c>
       <c r="B32" s="1" t="n"/>
@@ -4130,7 +4147,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="64" customHeight="1">
+    <row r="10" ht="78" customHeight="1">
       <c r="A10" s="26" t="inlineStr">
         <is>
           <t>1.5</t>
@@ -4214,7 +4231,7 @@
       <c r="AR10" s="56" t="n"/>
       <c r="AS10" s="15" t="inlineStr">
         <is>
-          <t>人工基準線。PoC 以作者本人照規範判兩輪示範（79 筆）：每顆 34.9 秒、漏判率 23.5%、對標準答案一致率 70.9%、重複性 87.2%、誤判率 2.3%（實際導入須以 3 位檢驗員重測）</t>
+          <t>人工基準線。PoC 以作者本人照規範判盲測集兩輪示範（80 筆，隔天）：每顆 46.7 秒、漏判率 22.2%、對標準答案一致率 77.5%、重複性 67.5%、誤判率 2.3%（實際導入須以 3 位檢驗員重測）</t>
         </is>
       </c>
       <c r="AT10" s="57" t="inlineStr">
@@ -4521,7 +4538,7 @@
       </c>
       <c r="C13" s="19" t="inlineStr">
         <is>
-          <t>② PoC 驗證（v1 未通過 → 規範 v2 重跑）</t>
+          <t>② PoC 驗證（v1 未通過 → v2 重跑 → v2.1 凍結後盲測）</t>
         </is>
       </c>
       <c r="D13" s="62" t="inlineStr">

--- a/docs/rollout/導入計畫.xlsx
+++ b/docs/rollout/導入計畫.xlsx
@@ -2305,8 +2305,8 @@
       </c>
       <c r="D29" s="37" t="inlineStr">
         <is>
-          <t>v1：0 批（L24 預警＝異常；完美判定亦未提早）
-v2、v2.1：尚未重新驗證</t>
+          <t>v1：0 批（L24 預警＝異常）
+v2.1：仍 0 批（L19 異常、L20 預警；異常比 v1 早 5 批發現）</t>
         </is>
       </c>
       <c r="E29" s="36" t="inlineStr">
@@ -2355,7 +2355,7 @@
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="38" t="inlineStr">
         <is>
-          <t>判讀（照實）：規範 v1 的 AI 漏判率 37.0%，比人工 23.5% 還高，② Gate（v1）未通過；規範 v2 重跑後 AI 每顆 8.2 秒（人工 34.9 秒）、漏判率 0%、重複性 92.5%、人工複判率 25.8% 達標，但評估者間一致率 82.5%、誤判率 7.6%（人工 2.3%）未達。規範 v2.1 凍結後在盲測集：AI 每顆 8.9 秒（人工 46.7 秒）、答對率 92.5%（人工 77.5%）、漏判 0%（人工 22.2%）、誤判 0%（人工 2.3%），評估者間一致率 87.5% 仍未達，預警提早尚未重驗 → Gate（v2.1）差一項、尚未通過。</t>
+          <t>判讀（照實）：規範 v1 的 AI 漏判率 37.0%，比人工 23.5% 還高，② Gate（v1）未通過；規範 v2 重跑後 AI 每顆 8.2 秒（人工 34.9 秒）、漏判率 0%、重複性 92.5%、人工複判率 25.8% 達標，但評估者間一致率 82.5%、誤判率 7.6%（人工 2.3%）未達。規範 v2.1 凍結後在盲測集：AI 每顆 8.9 秒（人工 46.7 秒）、答對率 92.5%（人工 77.5%）、漏判 0%（人工 22.2%）、誤判 0%（人工 2.3%），評估者間一致率 87.5% 仍未達；管制圖以 v2.1 判定誤差重跑後 L19 首次異常（v1 為 L24），預警仍未比異常提早 → Gate（v2.1）差一項、尚未通過。</t>
         </is>
       </c>
       <c r="B31" s="1" t="n"/>
@@ -5641,7 +5641,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="30" customHeight="1">
+    <row r="24" ht="64" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
         <is>
           <t>2.11</t>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="C24" s="15" t="inlineStr">
         <is>
-          <t>判異規則檢討與管制圖以 v2 實測誤差重新驗證</t>
+          <t>判異規則檢討與管制圖以實測判定誤差重新驗證</t>
         </is>
       </c>
       <c r="D24" s="26" t="inlineStr">
@@ -5725,7 +5725,7 @@
       <c r="AR24" s="56" t="n"/>
       <c r="AS24" s="15" t="inlineStr">
         <is>
-          <t>判異規則修訂、預警提早批數</t>
+          <t>結果（作品，2026-10-16 以 v2.1 盲測誤差重跑）：首次異常 L24 → L19（同完美判定），預警仍未比異常提早；試算只看崩角 u 圖 L17、前 16 批無誤報，待新資料驗證</t>
         </is>
       </c>
       <c r="AT24" s="26" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="H18" s="15" t="inlineStr">
         <is>
-          <t>【已觸發】25 批漂移情境模擬：首次預警＝首次異常＝L24，提早 0 批（完美判定亦未提早）；無人工複判時漂移完全未被偵出；基準期 L10 誤警報</t>
+          <t>【已觸發】25 批漂移情境模擬（v1 判定誤差）：首次預警＝首次異常＝L24，提早 0 批；無人工複判時漂移完全未被偵出；基準期 L10 誤警報。以 v2.1 判定誤差重跑：L19 首次異常、L20 預警，仍未提早</t>
         </is>
       </c>
       <c r="I18" s="15" t="inlineStr">
         <is>
-          <t>AI 判 Warning 之晶粒必送人工複判；以 v2 實測誤差重新驗證判異規則（2.11）</t>
+          <t>AI 判 Warning 之晶粒必送人工複判；以 v2.1 實測誤差重新驗證（2.11，已完成）；試只看崩角的管制圖（試算 L17），待新資料驗證</t>
         </is>
       </c>
       <c r="J18" s="15" t="inlineStr">
@@ -11410,7 +11410,7 @@
       </c>
       <c r="K14" s="15" t="inlineStr">
         <is>
-          <t>併入 2.11，以 v2 實測誤差重新模擬</t>
+          <t>2026-10-16 已以 v2.1 盲測誤差重跑：L19 首次異常，預警仍未提早；下一步試只看崩角的管制圖（試算 L17）</t>
         </is>
       </c>
     </row>
